--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -65,7 +65,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007A5C9E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -113,6 +118,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -556,13 +564,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -575,13 +583,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -594,13 +602,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -613,13 +621,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -632,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -651,13 +659,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +678,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -689,13 +697,13 @@
         <v>14</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -708,13 +716,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -727,13 +735,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -746,13 +754,13 @@
         <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -765,13 +773,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -784,13 +792,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -803,13 +811,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -822,13 +830,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -841,13 +849,13 @@
         <v>16</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -860,13 +868,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -879,13 +887,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -898,13 +906,13 @@
         <v>12</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -917,13 +925,13 @@
         <v>15</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -936,13 +944,13 @@
         <v>15</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -955,13 +963,13 @@
         <v>16</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -974,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -993,13 +1001,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -1012,13 +1020,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1031,13 +1039,13 @@
         <v>15</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1113,43 +1121,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SG01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1277,86 +1289,94 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SG01-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（成果物メタ）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>GET /outputs/{id} が 5xx</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. API を 500 でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>role=alert の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>UNWANTED critical</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SG01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（成果物メタ）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 成果物ビューア を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -1445,86 +1465,94 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SG01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（署名DL URL）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>GET /outputs/{id}/content-url が 5xx</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. API を 500 でモックし開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>role=alert の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>UNWANTED critical</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SG01-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（署名DL URL）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 成果物ビューア を開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -1613,129 +1641,141 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SG01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>取得失敗の inline error + toast（コメント）</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>GET /comments?target=workflow_output が 5xx</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. API を 500 でモックし開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>role=alert の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>UNWANTED critical</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SG01-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（コメント）</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 成果物ビューア を開く</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SG01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>「iframe(署名URL)」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 「iframe(署名URL)」を目視</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>html_path を署名URLの iframe で安全表示(XSS回避)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
@@ -1957,82 +1997,90 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>SG01-021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>未生成</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>HTML未生成 409 表示</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>html_path 無し</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. 未生成の成果物を開く</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>『まだ生成されていません』表示</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>SG01-022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -2125,43 +2173,47 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>SG01-025</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -2240,43 +2292,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SH01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. モックビューア を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2744,82 +2800,90 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SH01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>storage 未設定 503 表示</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>storage 未設定</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 未設定環境で開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>『保存先が未設定』表示</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SH01-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -2912,43 +2976,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SH01-017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -3027,43 +3095,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SI01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. タスクボード を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3277,129 +3349,141 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SI01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「▶再生」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「▶再生」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>ready/blocked カードで POST /tasks/{id}/play(dispatcher)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SI01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>「6列 lifecycle」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 「6列 lifecycle」を目視</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>backlog/ready/in_progress/awaiting/done/blocked にマップ（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SI01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>再生(play): 送信→反映</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 再生(play) を実行</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>POST /tasks/{id}/play 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>セクションG 貫通</t>
         </is>
@@ -3449,43 +3533,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SI01-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -3578,43 +3666,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SI01-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -3693,43 +3785,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SI02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3814,43 +3910,47 @@
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SI02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（詳細）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>GET /tasks/{id} が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -3982,43 +4082,47 @@
       <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SI02-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（受入条件）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>GET /tasks/{id}/acceptance-criteria が空配列</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -4150,43 +4254,47 @@
       <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SI02-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（実行履歴）</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>GET /tasks/{id}/executions が空配列</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -4318,43 +4426,47 @@
       <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SI02-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（コメント）</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>GET /comments?target=task が空配列</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -4447,43 +4559,47 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>SI02-019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>「概要/仕様/入出力/実行履歴/添付/コメント タブ」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. 「概要/仕様/入出力/実行履歴/添付/コメント タブ」を各クリック</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>対応タブ内容を表示(aria-selected/controls)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
@@ -4533,43 +4649,47 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>SI02-021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -4662,43 +4782,47 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>SI02-024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -4777,43 +4901,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SI03-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 実行モニタ(SSE) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5027,43 +5155,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SI03-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「ログストリーム」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「ログストリーム」を目視</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SSE で snapshot/status_change/end/error を逐次表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
@@ -5242,43 +5374,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SI03-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -5357,43 +5493,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SJ01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 承認インボックス を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5439,43 +5579,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SJ01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（承認待ち(5種統合/本人)）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 承認インボックス を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5607,129 +5751,141 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SJ01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「承認」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「承認」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>POST decide(approve)→インボックスから楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SJ01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>「差戻」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 「差戻」をクリック</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>POST decide(reject)→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SJ01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>承認/差戻(decide): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 承認/差戻(decide) を実行</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>POST /approval-inbox/{id}/decide 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN</t>
         </is>
@@ -5822,43 +5978,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SJ01-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -5951,43 +6111,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SJ01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -6066,43 +6230,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SK01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. ナレッジエクスプローラ を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6316,43 +6484,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SK01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「ツリーノード」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「ツリーノード」を展開/クリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>子ノード取得/詳細表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
@@ -6488,43 +6660,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SK01-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -6603,43 +6779,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SK02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 昇格レビュー を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6724,43 +6904,47 @@
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SK02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（昇格候補）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>GET /knowledge/promotions が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -7240,43 +7424,47 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SK02-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -7355,43 +7543,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SL01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. クライアント招待管理 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -7949,43 +8141,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SL01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -8078,43 +8274,47 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SL01-018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -8193,43 +8393,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SL02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. クライアントサインイン を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -8275,43 +8479,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SL02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（招待トークン）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>招待トークン の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -8353,43 +8561,47 @@
       <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SL02-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（表示名）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>表示名 の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -8431,86 +8643,94 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SL02-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「プロジェクトを開く」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「プロジェクトを開く」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>POST signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SL02-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>サインイン: 送信→反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. サインイン を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>POST /client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>セクションG 貫通</t>
         </is>
@@ -8732,43 +8952,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SL02-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -8847,43 +9071,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SA01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. サインイン/サインアップ を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -9085,86 +9313,94 @@
       <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SA01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「ログイン」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「ログイン」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>POST signin→atelier_access cookie→redirect（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SA01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>サインイン: 送信→反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. サインイン を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>POST /auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>セクションG 貫通</t>
         </is>
@@ -9214,43 +9450,47 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SA01-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>サインアップ: 送信→反映</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. サインアップ を実行</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>POST /auth/signup 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>セクションG 貫通</t>
         </is>
@@ -9429,86 +9669,94 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SA01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>セクションG G4</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SA01-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -9587,43 +9835,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SL03-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. クライアントプロジェクトビュー を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -9919,43 +10171,47 @@
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SL03-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -10048,43 +10304,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SL03-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -10163,43 +10423,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SM01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -10757,43 +11021,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SM01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -10872,43 +11140,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SO01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 自動スケジュール(cron) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11122,86 +11394,94 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SO01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「有効/無効トグル」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SO01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>有効トグル: 成功で即時反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 有効トグル を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN</t>
         </is>
@@ -11337,43 +11617,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SO01-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -11466,43 +11750,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SO01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -11581,43 +11869,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC36-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 通知センター を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -11663,43 +11955,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC36-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（承認待ち集約）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 通知センター を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11831,86 +12127,94 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TUC36-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「既読」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「既読」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>localStorage に記録→未読数減・未読フィルタ連動（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC36-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>「すべて/未読のみ タブ」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 「すべて/未読のみ タブ」を各クリック</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>フィルタ切替（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
@@ -12089,43 +12393,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TUC36-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -12175,86 +12483,94 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TUC36-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>状態永続</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ログイン済</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 画面で F5</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>セクションG G4</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TUC36-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -12333,43 +12649,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC37-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロフィール を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -12950,43 +13270,47 @@
       <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TUC37-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -13079,43 +13403,47 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TUC37-019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -13194,43 +13522,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC38-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -13487,43 +13819,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC38-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -13616,43 +13952,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TUC38-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -13731,43 +14071,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC39-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト切替 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -14024,43 +14368,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TUC39-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -14153,43 +14501,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TUC39-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -14268,43 +14620,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TUC40-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. グローバル検索 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -14350,82 +14706,90 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC40-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（横断検索）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. グローバル検索 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TUC40-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（横断検索）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>GET /search?q=&amp;kind= が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -14596,86 +14960,94 @@
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TUC40-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TUC40-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>「検索入力」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 「検索入力」を入力(debounce)</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>GET /search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
@@ -14725,43 +15097,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TUC40-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -14854,43 +15230,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TUC40-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -14969,43 +15349,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SA03-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース設定 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -15379,43 +15763,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SA03-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>名称保存(PATCH): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 名称保存(PATCH) を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>PATCH /workspaces/{id} + POST /account/ai-learning 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN</t>
         </is>
@@ -15465,43 +15853,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SA03-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>名称保存(PATCH): API 失敗時 inline error + toast</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>接続失敗/レート</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 名称保存(PATCH) を失敗させる</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>role=alert + toast、状態は不整合にならない</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>UNWANTED critical</t>
         </is>
@@ -15551,43 +15943,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SA03-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -15680,43 +16076,47 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SA03-018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -15795,43 +16195,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SB01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト一覧 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -15877,82 +16281,90 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SB01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（プロジェクト一覧(カーソル)）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト一覧 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SB01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>0 件時の空状態（プロジェクト一覧(カーソル)）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>GET /projects が空配列</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>セクションH</t>
         </is>
@@ -16045,129 +16457,141 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SB01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「プロジェクト行」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「プロジェクト行」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>/projects/s_b02?project=id へ遷移（死リンク修正済）（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SB01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>「前へ/次へ」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 「前へ/次へ」をクリック</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>カーソルページング（端で無効）（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SB01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>行クリックの遷移先が実在ルート</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 行をクリック</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>s_b02 ダッシュボードが開く（旧 /projects/{id}/dashboard 404 は #245 で修正）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>I4-S 死リンク検出→修正</t>
         </is>
@@ -16303,43 +16727,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SB01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -16418,43 +16846,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SB02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクトダッシュボード を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -16668,129 +17100,141 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SB02-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「KPI タイル」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「KPI タイル」を目視</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>現在フェーズ + タスク状態別件数を表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SB02-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>集計値=DB実数</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. task_counts を select count(*) と突合</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>内訳合計=総数・数字が DB と一致</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>セクションG G7</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SB02-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -16883,43 +17327,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SB02-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -16998,43 +17446,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SC01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 組織図 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -17248,129 +17700,141 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SC01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「社員ボタン」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「社員ボタン」をクリック</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>/employees/s_c02?employee=id へ遷移(編集)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SC01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>「部署セクション」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 「部署セクション」を目視</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>department 別に section 化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SC01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -17463,43 +17927,47 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SC01-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -17578,43 +18046,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SC02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 編集 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -17828,43 +18300,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SC02-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（display_name）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>display_name の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -17906,121 +18382,133 @@
       <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SC02-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（tone_preset）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>tone_preset の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SC02-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>入力フォーム</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>初期値/placeholder（custom_tone_text）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. フォームを開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>custom_tone_text の初期値/placeholder が正しい</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SC02-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>更新</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>保存(PATCH): 送信→反映</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>必須入力済</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 保存(PATCH) を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>PATCH /ai-employees/{id} 呼び出し→成功表示→別GET/DBに反映</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>セクションG 貫通</t>
         </is>
@@ -18238,43 +18726,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SC02-017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -18353,43 +18845,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SF01-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. 工程ワークフロー(司令塔) を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -18603,86 +19099,94 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SF01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「工程ノード/依存エッジ」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「工程ノード/依存エッジ」を目視</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>order 順ノード + 隣接エッジを描画（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SF01-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -18775,43 +19279,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SF01-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -18890,43 +19398,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>SF02-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>画面表示</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>画面が正常表示（全 UI 要素・モック準拠）</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. フェーズ管理 を開く</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -19140,86 +19652,94 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SF02-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>インタラクション</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>「状態 select」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 「状態 select」を変更</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>PATCH で状態遷移(done↔completed/blocked↔skipped 変換・楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>死にボタン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>SF02-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>状態遷移(select): 成功で即時反映</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>対象が存在</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. 状態遷移(select) を実行</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>PATCH /workflow/phases/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN</t>
         </is>
@@ -19312,43 +19832,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SF02-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>a11y</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. axe を実行</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>vitest-axe 実測済(該当時)</t>
         </is>
@@ -19441,43 +19965,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SF02-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>到達性</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -564,13 +564,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -583,13 +583,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -602,13 +602,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -621,13 +621,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -640,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -659,13 +659,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -678,13 +678,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>14</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -716,13 +716,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -735,13 +735,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -754,13 +754,13 @@
         <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -773,13 +773,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -792,13 +792,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -811,13 +811,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -830,13 +830,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -849,13 +849,13 @@
         <v>16</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -868,13 +868,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -887,13 +887,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -906,13 +906,13 @@
         <v>12</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -925,13 +925,13 @@
         <v>15</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -944,13 +944,13 @@
         <v>15</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -963,13 +963,13 @@
         <v>16</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -982,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1001,13 +1001,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1020,13 +1020,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1039,13 +1039,13 @@
         <v>15</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2087,45 +2087,49 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>SG01-023</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -2890,45 +2894,49 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SH01-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -3580,45 +3588,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SI01-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -4696,45 +4708,49 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>SI02-022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -5288,45 +5304,49 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SI03-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>実行モニタ(SSE)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -6025,45 +6045,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SJ01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -6574,45 +6598,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SK01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -7338,45 +7366,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SK02-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -8188,45 +8220,49 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SL01-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -8866,45 +8902,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SL02-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -9626,45 +9666,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SA01-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -10218,45 +10262,49 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SL03-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>クライアントプロジェクトビュー</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -10935,45 +10983,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SM01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>議事録アップロード</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -11664,45 +11716,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SO01-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -12440,45 +12496,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TUC36-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -13317,45 +13377,49 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>TUC37-017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -13866,45 +13930,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TUC38-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -14415,45 +14483,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TUC39-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -15144,45 +15216,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TUC40-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>グローバル検索</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -15990,45 +16066,49 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SA03-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -16641,45 +16721,49 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SB01-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -17241,45 +17325,49 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SB02-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -17841,45 +17929,49 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SC01-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -18640,45 +18732,49 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SC02-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -19193,45 +19289,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SF01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
@@ -19879,45 +19979,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>SF02-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>レスポンシブ</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. 各幅で開く</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>第8軸</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -583,13 +583,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -602,13 +602,13 @@
         <v>13</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -621,13 +621,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -640,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -659,13 +659,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -678,13 +678,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>14</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -735,13 +735,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -754,13 +754,13 @@
         <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -773,13 +773,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -811,13 +811,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -830,13 +830,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -849,13 +849,13 @@
         <v>16</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -868,13 +868,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -944,13 +944,13 @@
         <v>15</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -963,13 +963,13 @@
         <v>16</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -982,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1001,13 +1001,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1020,13 +1020,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2507,43 +2507,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SH01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（モック詳細）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで モックビューア を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -2675,43 +2679,47 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SH01-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（署名DL URL）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで モックビューア を開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -3314,43 +3322,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SI01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（タスク一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで タスクボード を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -4012,43 +4024,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SI02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（詳細）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで タスク詳細(6タブ) を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -4184,43 +4200,47 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SI02-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（受入条件）</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで タスク詳細(6タブ) を開く</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -4356,43 +4376,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>SI02-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（実行履歴）</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで タスク詳細(6タブ) を開く</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -4528,43 +4552,47 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>SI02-018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（コメント）</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで タスク詳細(6タブ) を開く</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -5728,43 +5756,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SJ01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（承認待ち(5種統合/本人)）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 承認インボックス を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -5912,43 +5944,47 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SJ01-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>承認インボックス</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>承認/差戻(decide): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. 承認/差戻(decide) を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN/rollback</t>
         </is>
@@ -6465,43 +6501,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SK01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（ナレッジツリー）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで ナレッジエクスプローラ を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -7022,43 +7062,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SK02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（昇格候補）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 昇格レビュー を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -7786,43 +7830,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SL01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（招待一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで クライアント招待管理 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -11403,43 +11451,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SO01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（スケジュール一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -11540,43 +11592,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SO01-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>有効トグル: 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 有効トグル を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN/rollback</t>
         </is>
@@ -12140,43 +12196,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC36-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>通知センター</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（承認待ち集約）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 通知センター を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -12920,43 +12980,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC37-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（自己プロフィール）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで プロフィール を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -13797,43 +13861,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC38-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（所属 WS 一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで ワークスペース切替 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -14350,43 +14418,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TUC39-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（現在WS内プロジェクト）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで プロジェクト切替 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -15636,43 +15708,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SA03-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（WS 詳細）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで ワークスペース設定 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -16494,43 +16570,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SB01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロジェクト一覧</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（プロジェクト一覧(カーソル)）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで プロジェクト一覧 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -17141,43 +17221,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SB02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（KPI ダッシュボード）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで プロジェクトダッシュボード を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -17745,43 +17829,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SC01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（AI 社員一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで AI社員 組織図 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -18349,43 +18437,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SC02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（社員詳細）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで AI社員 編集 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -19152,43 +19244,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SF01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（工程一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで 工程ワークフロー(司令塔) を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -19709,43 +19805,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SF02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>403 拒否表示（工程一覧）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 権限なしで フェーズ管理 を開く</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>セクションG 越境</t>
         </is>
@@ -19846,43 +19946,47 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SF02-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>楽観更新</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>状態遷移(select): 失敗でロールバック</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>サーバ 4xx/5xx</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. 状態遷移(select) を実行しAPIが失敗</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>楽観反映が元に戻り、inline error + toast を表示</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>EVENT-DRIVEN/rollback</t>
         </is>

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -1,39 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA01_サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA03_ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB01_プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB02_プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SC01_AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SC02_AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SF01_工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SF02_フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SG01_成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH01_モックビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SI01_タスクボード" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SI02_タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SI03_実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SJ01_承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SK01_ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SK02_昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL01_クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL02_クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL03_クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SM01_議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO01_自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC36_通知センター" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC37_プロフィール" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC38_ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC39_プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC40_グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SA01_サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SA03_ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SB01_プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SB02_プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SC01_AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SC02_AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SF01_工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SF02_フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SG01_成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SH01_モックビューア" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SI01_タスクボード" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SI02_タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SI03_実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SJ01_承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="SK01_ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SK02_昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SL01_クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SL02_クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SL03_クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SM01_議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="SO01_自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TUC36_通知センター" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="TUC37_プロフィール" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TUC40_グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,13 +583,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -621,13 +621,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -640,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -659,13 +659,13 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -678,13 +678,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>14</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -716,13 +716,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -735,13 +735,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -754,13 +754,13 @@
         <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -773,13 +773,13 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -830,13 +830,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -849,13 +849,13 @@
         <v>16</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -868,13 +868,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -944,13 +944,13 @@
         <v>15</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1001,13 +1001,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1020,13 +1020,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1207,43 +1207,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SG01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（成果物メタ）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1383,43 +1387,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SG01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（署名DL URL）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1559,43 +1567,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SG01-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>成果物ビューア</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（コメント）</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. 成果物ビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2382,43 +2394,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SH01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（モック詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. モックビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2554,43 +2570,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SH01-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>モックビューア</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（署名DL URL）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. モックビューア を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3197,43 +3217,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SI01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>タスクボード</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（タスク一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. タスクボード を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3895,43 +3919,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SI02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4071,43 +4099,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SI02-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（受入条件）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4247,43 +4279,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>SI02-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（実行履歴）</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4423,43 +4459,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>SI02-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>タスク詳細(6タブ)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（コメント）</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. タスク詳細(6タブ) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6376,43 +6416,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SK01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ナレッジエクスプローラ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（ナレッジツリー）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. ナレッジエクスプローラ を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -6933,43 +6977,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SK02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>昇格レビュー</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（昇格候補）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 昇格レビュー を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7705,43 +7753,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SL01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>クライアント招待管理</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（招待一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. クライアント招待管理 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11326,43 +11378,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SO01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>自動スケジュール(cron)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（スケジュール一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -12855,43 +12911,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC37-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロフィール</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（自己プロフィール）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロフィール を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -13736,43 +13796,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC38-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ワークスペース切替</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -14293,43 +14357,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TUC39-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロジェクト切替</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（現在WS内プロジェクト）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクト切替 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -15583,43 +15651,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SA03-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ワークスペース設定</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（WS 詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. ワークスペース設定 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -17096,43 +17168,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SB02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>プロジェクトダッシュボード</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（KPI ダッシュボード）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. プロジェクトダッシュボード を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -17704,43 +17780,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SC01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>AI社員 組織図</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（AI 社員一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 組織図 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -18312,43 +18392,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SC02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>AI社員 編集</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（社員詳細）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. AI社員 編集 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -19119,43 +19203,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SF01-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>工程ワークフロー(司令塔)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（工程一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. 工程ワークフロー(司令塔) を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -19680,43 +19768,47 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>SF02-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>フェーズ管理</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>loading skeleton 表示（工程一覧）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. フェーズ管理 を開き取得完了前を観察</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -564,13 +564,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -887,13 +887,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -8658,43 +8658,47 @@
       <c r="I4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SL02-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>招待トークン: 必須/最小10</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. 招待トークン に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -8740,43 +8744,47 @@
       <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SL02-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>クライアントサインイン</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>表示名: 任意</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. 表示名 に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -9336,43 +9344,47 @@
       <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SA01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>email: 必須/型/最大200</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. email に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -9414,43 +9426,47 @@
       <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>SA01-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>サインイン/サインアップ</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>password: 必須/型</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. password に不正値/未入力を入れる</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>エラー表示 かつ 送信ボタン無効</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -1,39 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA01_サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA03_ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB01_プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB02_プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SC01_AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SC02_AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SF01_工程ワークフロー(司令塔)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SF02_フェーズ管理" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SG01_成果物ビューア" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH01_モックビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SI01_タスクボード" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SI02_タスク詳細(6タブ)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SI03_実行モニタ(SSE)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SJ01_承認インボックス" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SK01_ナレッジエクスプローラ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SK02_昇格レビュー" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL01_クライアント招待管理" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL02_クライアントサインイン" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SL03_クライアントプロジェクトビュー" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SM01_議事録アップロード" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO01_自動スケジュール(cron)" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC36_通知センター" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC37_プロフィール" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC38_ワークスペース切替" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC39_プロジェクト切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUC40_グローバル検索" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SA01_サインインサインアップ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SA03_ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SB01_プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SB02_プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SC01_AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SC02_AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SE01_チャット" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SF01_工程ワークフロー(司令塔)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SF02_フェーズ管理" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SG01_成果物ビューア" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SH01_モックビューア" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SI01_タスクボード" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SI02_タスク詳細(6タブ)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SI03_実行モニタ(SSE)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="SJ01_承認インボックス" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SK01_ナレッジエクスプローラ" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SK02_昇格レビュー" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SL01_クライアント招待管理" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SL02_クライアントサインイン" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SL03_クライアントプロジェクトビュー" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="SM01_議事録アップロード" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="SO01_自動スケジュール(cron)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="TUC36_通知センター" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TUC37_プロフィール" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TUC40_グローバル検索" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,10 +608,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -626,10 +627,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -679,33 +680,33 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>工程ワークフロー(司令塔)(SF01)</t>
+          <t>チャット(SE01)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>フェーズ管理(SF02)</t>
+          <t>工程ワークフロー(司令塔)(SF01)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -717,14 +718,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>成果物ビューア(SG01)</t>
+          <t>フェーズ管理(SF02)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
@@ -736,14 +737,14 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>モックビューア(SH01)</t>
+          <t>成果物ビューア(SG01)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -755,14 +756,14 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>タスクボード(SI01)</t>
+          <t>モックビューア(SH01)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -774,14 +775,14 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>タスク詳細(6タブ)(SI02)</t>
+          <t>タスクボード(SI01)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
@@ -793,17 +794,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>実行モニタ(SSE)(SI03)</t>
+          <t>タスク詳細(6タブ)(SI02)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
@@ -812,17 +813,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>承認インボックス(SJ01)</t>
+          <t>実行モニタ(SSE)(SI03)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
@@ -831,14 +832,14 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>ナレッジエクスプローラ(SK01)</t>
+          <t>承認インボックス(SJ01)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
@@ -850,14 +851,14 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>昇格レビュー(SK02)</t>
+          <t>ナレッジエクスプローラ(SK01)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
@@ -869,14 +870,14 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>クライアント招待管理(SL01)</t>
+          <t>昇格レビュー(SK02)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -888,14 +889,14 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>クライアントサインイン(SL02)</t>
+          <t>クライアント招待管理(SL01)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -907,14 +908,14 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>クライアントプロジェクトビュー(SL03)</t>
+          <t>クライアントサインイン(SL02)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
@@ -926,17 +927,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>議事録アップロード(SM01)</t>
+          <t>クライアントプロジェクトビュー(SL03)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
@@ -945,17 +946,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)(SO01)</t>
+          <t>議事録アップロード(SM01)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
@@ -964,14 +965,14 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>通知センター(TUC36)</t>
+          <t>自動スケジュール(cron)(SO01)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>0</v>
@@ -983,14 +984,14 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>プロフィール(TUC37)</t>
+          <t>通知センター(TUC36)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
@@ -1002,14 +1003,14 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替(TUC38)</t>
+          <t>プロフィール(TUC37)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1021,7 +1022,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替(TUC39)</t>
+          <t>ワークスペース切替(TUC38)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -1040,19 +1041,38 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索(TUC40)</t>
+          <t>プロジェクト切替(TUC39)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索(TUC40)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,6 +1082,728 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SF02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. フェーズ管理 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SF02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SF02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. フェーズ管理 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SF02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /workflow/phases?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SF02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /workflow/phases?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SF02-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで フェーズ管理 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SF02-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「状態 select」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「状態 select」を変更</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>PATCH で状態遷移(done↔completed/blocked↔skipped 変換・楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SF02-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移(select): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 状態遷移(select) を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /workflow/phases/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SF02-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移(select): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 状態遷移(select) を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SF02-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>状態遷移(select): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 状態遷移(select) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SF02-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SF02-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SF02-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SF02-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ管理</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2288,7 +3030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3143,13 +3885,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3860,12 +4602,294 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SI01-101</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>モック準拠の全領域 (選択バー/ツールバー/機能別グループ×6レーン/凡例一致レーン名)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>design-audit R5</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. /tasks を開く</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>選択バー(選択時)・表示/分類/絞込ツールバー・グループごとの6レーンが表示。レーン名=凡例と同一語 (旧: バックログ/実行可/進行中/ブロックの不一致を修正)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ 2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SI01-102</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>選択→「選択を再生する」一括再生（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ready タスク2件</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. checkbox 2件選択 2. 選択を再生する</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>選択バーに「2件・合計見積7時間」→ POST /tasks/{id}/play ×2 → 実装中レーンへ移動し「AI 社員が実装中・spawning」表示 (DB: dispatch_status=spawning 確認)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>実操作+DB突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SI01-103</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>タスクを追加モーダル（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. タスクを追加→入力→作成</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>実 POST /tasks → 新分類グループ (requirements) が即出現</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>実操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SI01-104</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>かんばん/リスト切替・分類切替 (機能別/担当AI別/フェーズ別/なし)・絞り込み</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 各トグルを操作</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>リスト=テーブル表示・分類ごとに再グルーピング・絞込で実フィルタ</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SI01-105</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>カードに見積時間 (未見積)・ID・担当・blocked_reason・dispatch 状態</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. 各カード確認</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>実フィールドを表示。捏造値なし</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>実操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SI01-106</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>タスクボード</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>モックの「依存グラフ」ビューは非表示</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示トグル確認</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>タスク依存 API が無いため出さない (GAP-006 起票)</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>意図的差分</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5045,7 +6069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5677,7 +6701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6446,7 +7470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7027,7 +8051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7843,7 +8867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8743,716 +9767,6 @@
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SL02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアントサインイン を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SL02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SL02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（招待トークン）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>招待トークン の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SL02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>招待トークン: 必須/最小10</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. 招待トークン に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SL02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（表示名）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>表示名 の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SL02-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>表示名: 任意</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名 に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SL02-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「プロジェクトを開く」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「プロジェクトを開く」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>POST signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SL02-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>サインイン: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. サインイン を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>POST /client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 貫通</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SL02-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>サインイン: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. サインイン を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SL02-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>認証</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>401 invalid/410 expired 文言化</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>無効/期限切れトークン</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 無効トークンで送信</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>401→『招待トークンが無効』/410→『有効期限切れ』</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>R-T08 別認証系</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SL02-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SL02-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SL02-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SL02-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>クライアントサインイン</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -10273,6 +10587,716 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SL02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアントサインイン を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SL02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SL02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（招待トークン）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>招待トークン の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SL02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>招待トークン: 必須/最小10</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 招待トークン に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SL02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（表示名）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>表示名 の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SL02-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>表示名: 任意</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名 に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SL02-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトを開く」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「プロジェクトを開く」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>POST signin→client_portal cookie→/client/s_l03 遷移（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SL02-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>サインイン: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. サインイン を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>POST /client/auth/signin 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 貫通</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SL02-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>サインイン: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. サインイン を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SL02-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>認証</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>401 invalid/410 expired 文言化</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>無効/期限切れトークン</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 無効トークンで送信</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>401→『招待トークンが無効』/410→『有効期限切れ』</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>R-T08 別認証系</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SL02-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SL02-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SL02-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SL02-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>クライアントサインイン</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10881,779 +11905,6 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SM01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SM01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SM01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>transcribe 依存 (実 Whisper 外部APIキー)。解除: キー設定+実mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SM01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>GET /meetings/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>SM01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>GET /meetings/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>SM01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>403 拒否表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SM01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「ファイル選択」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「ファイル選択」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>SM01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>upload-url→PUT→POST /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>同上 (upload-url→実PUT 200 までは v4/v11 PASS 済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>SM01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>SM01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>G3実副作用</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>実 storage/Whisper 副作用(BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>実DB/実storage</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1. 実ファイルをアップロード</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>実 Whisper 外部APIキー。解除: キー設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>SM01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>マルチターン</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>queued→parsing→done の状態継続</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>アップロード後</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>1. 完了までポーリングを観察</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>transcribe 状態遷移は Whisper 依存。解除: 同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SM01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SM01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SM01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SM01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -11734,12 +11985,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SO01-001</t>
+          <t>SM01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -11759,7 +12010,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 自動スケジュール(cron) を開く</t>
+          <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -11777,12 +12028,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SO01-002</t>
+          <t>SM01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -11822,198 +12073,202 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SO01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SM01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. 議事録アップロード を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>transcribe 依存 (実 Whisper 外部APIキー)。解除: キー設定+実mp3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SO01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SM01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /cron-schedules?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GET /meetings/{id} が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SO01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SM01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /cron-schedules?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>GET /meetings/{id} が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. API を 500 でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>role=alert の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SO01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SM01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>403 拒否表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 議事録アップロード を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SO01-007</t>
+          <t>SM01-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -12023,7 +12278,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
+          <t>「ファイル選択」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -12033,12 +12288,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「有効/無効トグル」をクリック</t>
+          <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -12053,202 +12308,202 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SO01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SM01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>upload-url→PUT→POST /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>同上 (upload-url→実PUT 200 までは v4/v11 PASS 済)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SO01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SM01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SO01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SM01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>G3実副作用</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>実 storage/Whisper 副作用(BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>実DB/実storage</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. 実ファイルをアップロード</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>実 Whisper 外部APIキー。解除: キー設定</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SO01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>即時実行ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>run-now API 無しのため列非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>API欠如</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SM01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>マルチターン</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>queued→parsing→done の状態継続</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>アップロード後</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>1. 完了までポーリングを観察</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>transcribe 状態遷移は Whisper 依存。解除: 同上</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SO01-012</t>
+          <t>SM01-012</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -12290,12 +12545,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SO01-013</t>
+          <t>SM01-013</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -12337,12 +12592,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SO01-014</t>
+          <t>SM01-014</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -12384,12 +12639,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SO01-015</t>
+          <t>SM01-015</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -12434,6 +12689,775 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SO01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SO01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SO01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SO01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /cron-schedules?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SO01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /cron-schedules?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SO01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SO01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「有効/無効トグル」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SO01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SO01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SO01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>即時実行ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>run-now API 無しのため列非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>API欠如</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SO01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SO01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SO01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SO01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13155,7 +14179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14082,587 +15106,6 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -14743,12 +15186,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -14768,7 +15211,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -14786,12 +15229,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -14833,12 +15276,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -14848,7 +15291,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -14858,7 +15301,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -14876,12 +15319,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -14891,12 +15334,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が空配列</t>
+          <t>GET /workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -14923,12 +15366,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -14938,12 +15381,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が 5xx</t>
+          <t>GET /workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -14970,12 +15413,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-006</t>
+          <t>TUC38-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -14985,7 +15428,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（現在WS内プロジェクト）</t>
+          <t>403 拒否表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -14995,7 +15438,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで プロジェクト切替 を開く</t>
+          <t>1. 権限なしで ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -15017,12 +15460,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -15032,7 +15475,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -15042,12 +15485,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -15064,12 +15507,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -15111,12 +15554,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-009</t>
+          <t>TUC38-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -15158,12 +15601,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -15205,12 +15648,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -15255,6 +15698,587 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16919,7 +17943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17583,6 +18607,241 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB01-101</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>バグ修正</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>フェーズバッジが実工程と一致 (常に「ヒアリング中」固定だったバグ)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>工程が要件定義まで進行</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧カードのバッジを確認</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>「要件定義中」+ 進捗バー 2/9 (原因: API が日本語工程名を英語キー検証で hearing に落としていた → 変換辞書で修正)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>実操作+API curl 突合 2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB01-102</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>新規プロジェクト作成モーダル（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 新規プロジェクト→名前入力→作成</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>実 POST /projects → 一覧に即出現・工程 seed 済 (工程1/9・たった今更新)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>実操作: 「社内ナレッジポータル構築」を実作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB01-103</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>検索フィルタ + すべて/進行中/アーカイブ タブ（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>2件以上</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 「EC」を入力 2. タブ切替</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>名前/クライアント/フェーズで実絞込・クリア×ボタン表示</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SB01-104</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>カードクリック → ダッシュボード遷移</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. カードをクリック</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>/projects/dashboard?project=&lt;id&gt; へ遷移 (project 文脈維持)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>実操作: URL 遷移確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SB01-105</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト一覧</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>更新時刻がモック準拠の相対表記</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. カード右下を確認</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>「9 時間前更新」「たった今更新」(旧: 絶対日付)</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17594,7 +18853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18208,6 +19467,335 @@
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB02-101</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>モック準拠の全領域再構築 (kicker+h1+サブタイトル / KPI4枚 / 工程+リンク / 活動タイムライン / 右レール3カード)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>design-audit R3</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. /projects/dashboard を開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>モック S-B02-dashboard.html の全領域が実データで表示</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ 2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB02-102</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>全体進捗率 = 実 phases 完了率 / 未承認 INBOX = 実 approval-inbox / 確定事項 = 実 decisions</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>実データ有</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. KPI を DB 値と突合</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>11% (1/9)・INBOX 1・確定 6/未確認 3 が実 API 値と一致</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (curl 突合)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB02-103</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>承認リクエストの「承認」ボタン（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>pending 承認有</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認をクリック</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>POST /approval-inbox/{id}/decide が発火し DB status=approved・カード消滅・INBOX KPI が 1→0 に即時反映</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>実操作: resolved_at を API で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB02-104</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>「工程画面で確定事項・成果物を見る」「フェーズ管理」「チャットで依頼」「成果物」各リンク（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 各リンクを確認</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>?project= 付きの実ルートへの href が存在 (死にリンク無し)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>href 検証。遷移クリック実走は planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SB02-105</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>最新の活動 = decisions/outputs/threads/工程完了 の実タイムスタンプ降順合成</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>実データ有</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. タイムラインを確認</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>実データ 8 件が時刻降順・社員アバター付きで表示。捏造行なし</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SB02-106</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 3 幅で撮影</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>単一カラム積層・横スクロールなし (工程のみ意図的横スクロール)</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ 3幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SB02-107</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクトダッシュボード</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>モックの「未解決コメント」KPI は「確定事項」に置換</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. KPI 4 枚目を確認</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト横断コメント API 不在のため実データ KPI に置換 (GAP-005 起票)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>意図的差分・gap-tracker 記載</t>
         </is>
       </c>
     </row>
@@ -19693,6 +21281,1010 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SE01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>3ペイン構成が正常表示（モック S-E01-thread.html 準拠: 左260px スレッド/中央チャット/右340px コンテキスト）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済+スレッド有</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>3ペインが描画され、モックの主要領域(スレッド検索/新規スレッド/工程グルーピング/工程文脈バー/社員ヘッダー/コンポーザ/右タブ)が全て存在</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ (design-audit R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SE01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-*/--rounded-* トークン準拠・社員カラーはモック avatar-* 準拠</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>スクショ照合済</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SE01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>スレッド一覧が実 API (GET /chat/threads?project_id) から描画</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 開いて一覧を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>実スレッドが工程グルーピング(現在→完了→横断)で表示・message_count/相対時刻付き</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SE01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>スレッド0件時の空状態</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>スレッド0件</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1. 空プロジェクトで開く</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>「スレッドがありません…」の empty state (500 にならない)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SE01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>送信失敗時のエラーバナー(単一・dismiss可)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>LLM 未設定 or API 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. メッセージ送信</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザ直上に role=alert バナー1箇所のみ・✕で閉じる・スレッド切替でリセット</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (二重表示バグ修正済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SE01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド検索フィルタ（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド複数</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に「競合」入力</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>タイトル/社員名/最終メッセージで絞り込まれる</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SE01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>スレッド切替・新規スレッド作成（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 別スレッドをクリック 2. 新規スレッドで作成</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>メッセージが切替わる/POST /chat/threads (phase_id 任意) で作成され選択される</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>切替=実操作・作成=vitest 配線試験</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SE01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ペイン開閉トグル（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 左右トグルを各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>左ペイン/右ペインが開閉し grid が追従・aria-pressed 反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SE01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ送信 (Enter=送信 / Shift+Enter=改行 / IME 変換中は送信しない)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>スレッド選択済</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 入力して Enter</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>user バブル即時表示→SSE 応答 (LLM 無環境では誠実なエラー表示)・IME 変換確定 Enter で誤送信しない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Enter 送信=実操作。IME は目視未 (JSDOM 契約のみ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SE01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>@メンション ピッカー（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員複数</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. @メンション をクリック 2. 社員を選択</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>実 AI 社員一覧(対話相手は除外)が出て、カーソル位置に「@名前 」が挿入される</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>実操作: textarea="この件、@ワンダ " を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SE01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナレッジ参照ピッカー（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. ナレッジ参照をクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>実ナレッジ一覧から選択で「[ナレッジ: title] 」挿入。0件時は「まだありません+自動RAGは常時有効」の誠実表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (0件経路)。1件以上経路は planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SE01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>死に要素ゼロ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザに非機能ボタンが存在しない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. コンポーザの全ボタンを列挙</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>添付・/コマンドのボタンは**描画されない**(gap tracker 起票済)。表示される全ボタンが機能する</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>実操作: 添付=0個・/コマンド=0個 を機械確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SE01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>tool ロールメッセージのツールカード描画</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tool メッセージ有</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 該当スレッドを開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>monospace ツール名ヘッダ+本文カード (モック .tool-card 準拠)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SE01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>工程文脈バー (現在の工程・Stage n/9・工程画面リンク)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. ヘッダーを確認 2. リンクをクリック</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>実 current_phase を表示し /workflow?project= へ遷移</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>表示=実操作。遷移クリックは planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SE01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>右ペイン: 主力決定/コンテキスト/参照タブ</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>decisions 有</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各タブをクリック</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>実 /decisions の確定カード(反映先付)・F-CTX01 実測値(SSE context)・実 /knowledge 一覧</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>主力決定=実操作。コンテキスト/参照タブ切替クリックは planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SE01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>履歴</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>リロードで会話が消えない (既存メッセージロード)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ有</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. F5</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>過去メッセージが created_at 付きで再表示</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (バグ#23 回帰)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SE01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない・モバイルは一覧⇄チャット切替</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く 2. モバイルで戻るボタン</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し・モバイルで戻る→一覧表示・右ペインは重ね表示トグル</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ 3幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SE01-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>axe 0 critical/serious・log role/aria-live/label 契約</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. axe 実行</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>違反0・role=log aria-live=polite・「メッセージを入力」label</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>vitest 契約試験 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>SE01-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>他 WS ユーザーのスレッドが見えない (RLS)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>別WSユーザー</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>1. 別アカウントで開く</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>一覧に出ない・直接 ID アクセスは 404</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>セクションG 越境 (API 層は test_chat.py で PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SE01-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>?thread= URL で直接スレッドを開ける</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat?thread=&lt;id&gt; を開く</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>該当スレッドが選択状態で開く</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (監査スクリプトの起動経路)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20266,726 +22858,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SF02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. フェーズ管理 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SF02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SF02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. フェーズ管理 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SF02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /workflow/phases?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SF02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /workflow/phases?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SF02-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで フェーズ管理 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SF02-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「状態 select」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「状態 select」を変更</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>PATCH で状態遷移(done↔completed/blocked↔skipped 変換・楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SF02-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>状態遷移(select): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 状態遷移(select) を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /workflow/phases/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SF02-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>状態遷移(select): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 状態遷移(select) を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SF02-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>状態遷移(select): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 状態遷移(select) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SF02-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SF02-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SF02-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SF02-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>フェーズ管理</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -12,29 +12,30 @@
     <sheet name="SA03_ワークスペース設定" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="SB01_プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SB02_プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SC01_AI社員 組織図" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SC02_AI社員 編集" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SE01_チャット" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SF01_工程ワークフロー(司令塔)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SF02_フェーズ管理" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SG01_成果物ビューア" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="SH01_モックビューア" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="SI01_タスクボード" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SI02_タスク詳細(6タブ)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SI03_実行モニタ(SSE)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="SJ01_承認インボックス" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SK01_ナレッジエクスプローラ" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="SK02_昇格レビュー" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="SL01_クライアント招待管理" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="SL02_クライアントサインイン" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="SL03_クライアントプロジェクトビュー" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="SM01_議事録アップロード" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="SO01_自動スケジュール(cron)" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="TUC36_通知センター" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="TUC37_プロフィール" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="TUC38_ワークスペース切替" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="TUC39_プロジェクト切替" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="TUC40_グローバル検索" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="SB03_プロジェクト設定" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SC01_AI社員 組織図" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SC02_AI社員 編集" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SE01_チャット" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SF01_工程ワークフロー(司令塔)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SF02_フェーズ管理" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SG01_成果物ビューア" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SH01_モックビューア" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SI01_タスクボード" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SI02_タスク詳細(6タブ)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="SI03_実行モニタ(SSE)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SJ01_承認インボックス" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SK01_ナレッジエクスプローラ" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SK02_昇格レビュー" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SL01_クライアント招待管理" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SL02_クライアントサインイン" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="SL03_クライアントプロジェクトビュー" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="SM01_議事録アップロード" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="SO01_自動スケジュール(cron)" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TUC36_通知センター" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="TUC37_プロフィール" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="TUC40_グローバル検索" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -642,14 +643,14 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AI社員 組織図(SC01)</t>
+          <t>プロジェクト設定(SB03)</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -661,14 +662,14 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AI社員 編集(SC02)</t>
+          <t>AI社員 組織図(SC01)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -680,33 +681,33 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>チャット(SE01)</t>
+          <t>AI社員 編集(SC02)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>工程ワークフロー(司令塔)(SF01)</t>
+          <t>チャット(SE01)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -718,14 +719,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>フェーズ管理(SF02)</t>
+          <t>工程ワークフロー(司令塔)(SF01)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
@@ -737,14 +738,14 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>成果物ビューア(SG01)</t>
+          <t>フェーズ管理(SF02)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -756,14 +757,14 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>モックビューア(SH01)</t>
+          <t>成果物ビューア(SG01)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -775,14 +776,14 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>タスクボード(SI01)</t>
+          <t>モックビューア(SH01)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
@@ -794,14 +795,14 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>タスク詳細(6タブ)(SI02)</t>
+          <t>タスクボード(SI01)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0</v>
@@ -813,17 +814,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>実行モニタ(SSE)(SI03)</t>
+          <t>タスク詳細(6タブ)(SI02)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
@@ -832,17 +833,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>承認インボックス(SJ01)</t>
+          <t>実行モニタ(SSE)(SI03)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -851,14 +852,14 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>ナレッジエクスプローラ(SK01)</t>
+          <t>承認インボックス(SJ01)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
@@ -870,14 +871,14 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>昇格レビュー(SK02)</t>
+          <t>ナレッジエクスプローラ(SK01)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -889,14 +890,14 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>クライアント招待管理(SL01)</t>
+          <t>昇格レビュー(SK02)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -908,14 +909,14 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>クライアントサインイン(SL02)</t>
+          <t>クライアント招待管理(SL01)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
@@ -927,14 +928,14 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>クライアントプロジェクトビュー(SL03)</t>
+          <t>クライアントサインイン(SL02)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
@@ -946,17 +947,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>議事録アップロード(SM01)</t>
+          <t>クライアントプロジェクトビュー(SL03)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
@@ -965,17 +966,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)(SO01)</t>
+          <t>議事録アップロード(SM01)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
@@ -984,14 +985,14 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>通知センター(TUC36)</t>
+          <t>自動スケジュール(cron)(SO01)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
@@ -1003,14 +1004,14 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>プロフィール(TUC37)</t>
+          <t>通知センター(TUC36)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1022,14 +1023,14 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替(TUC38)</t>
+          <t>プロフィール(TUC37)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -1041,7 +1042,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替(TUC39)</t>
+          <t>ワークスペース切替(TUC38)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1060,19 +1061,38 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索(TUC40)</t>
+          <t>プロジェクト切替(TUC39)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索(TUC40)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1082,6 +1102,587 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SF01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 工程ワークフロー(司令塔) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SF01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SF01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 工程ワークフロー(司令塔) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SF01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /workflow/phases?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SF01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /workflow/phases?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SF01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（工程一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 工程ワークフロー(司令塔) を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SF01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「工程ノード/依存エッジ」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「工程ノード/依存エッジ」を目視</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>order 順ノード + 隣接エッジを描画（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SF01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SF01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SF01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SF01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>工程ワークフロー(司令塔)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1803,7 +2404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3030,7 +3631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3885,7 +4486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4889,7 +5490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6069,7 +6670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6701,7 +7302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7470,7 +8071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8051,7 +8652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8857,916 +9458,6 @@
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SL01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアント招待管理 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SL01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SL01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. クライアント招待管理 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SL01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /client-invitations?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SL01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /client-invitations?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SL01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（招待一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで クライアント招待管理 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SL01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「招待を発行」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「招待を発行」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>POST→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SL01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>「失効」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 「失効」をクリック</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>POST revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SL01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>発行(POST): 送信→反映</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 発行(POST) を実行</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>POST /client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 貫通</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SL01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>発行(POST): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 発行(POST) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SL01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>失効(revoke): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 失効(revoke) を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>POST /client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SL01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>失効(revoke): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 失効(revoke) を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SL01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>失効(revoke): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 失効(revoke) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SL01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>再送ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>resend API 無しのため非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>API欠如</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SL01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SL01-016</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SL01-017</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SL01-018</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>クライアント招待管理</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -10587,6 +10278,916 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SL01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント招待管理 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SL01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SL01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント招待管理 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SL01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /client-invitations?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SL01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /client-invitations?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SL01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（招待一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで クライアント招待管理 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SL01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「招待を発行」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「招待を発行」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>POST→raw token を1度だけバナー表示(R-T08 再取得不可)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SL01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>「失効」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 「失効」をクリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>POST revoke(楽観)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SL01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>発行(POST): 送信→反映</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 発行(POST) を実行</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>POST /client-invitations 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 貫通</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SL01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>発行(POST): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 発行(POST) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SL01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>POST /client-invitations/{id}/revoke 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SL01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SL01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>失効(revoke): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 失効(revoke) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SL01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>再送ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>resend API 無しのため非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>API欠如</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SL01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SL01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SL01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SL01-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>クライアント招待管理</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11291,7 +11892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11905,779 +12506,6 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SM01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SM01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SM01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>transcribe 依存 (実 Whisper 外部APIキー)。解除: キー設定+実mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SM01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>GET /meetings/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>SM01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>GET /meetings/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>SM01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>403 拒否表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SM01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「ファイル選択」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「ファイル選択」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>SM01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>upload-url→PUT→POST /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>同上 (upload-url→実PUT 200 までは v4/v11 PASS 済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>SM01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>SM01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>G3実副作用</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>実 storage/Whisper 副作用(BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>実DB/実storage</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1. 実ファイルをアップロード</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>実 Whisper 外部APIキー。解除: キー設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>SM01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>マルチターン</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>queued→parsing→done の状態継続</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>アップロード後</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>1. 完了までポーリングを観察</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>transcribe 状態遷移は Whisper 依存。解除: 同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SM01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SM01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SM01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SM01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -12758,12 +12586,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SO01-001</t>
+          <t>SM01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -12783,7 +12611,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 自動スケジュール(cron) を開く</t>
+          <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -12801,12 +12629,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SO01-002</t>
+          <t>SM01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -12846,198 +12674,202 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SO01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SM01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. 議事録アップロード を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>transcribe 依存 (実 Whisper 外部APIキー)。解除: キー設定+実mp3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SO01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SM01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /cron-schedules?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GET /meetings/{id} が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SO01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SM01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /cron-schedules?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>GET /meetings/{id} が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. API を 500 でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>role=alert の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SO01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SM01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>403 拒否表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 議事録アップロード を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SO01-007</t>
+          <t>SM01-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13047,7 +12879,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
+          <t>「ファイル選択」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -13057,12 +12889,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「有効/無効トグル」をクリック</t>
+          <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -13077,202 +12909,202 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SO01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SM01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>upload-url→PUT→POST /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>同上 (upload-url→実PUT 200 までは v4/v11 PASS 済)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SO01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SM01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SO01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SM01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>G3実副作用</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>実 storage/Whisper 副作用(BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>実DB/実storage</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. 実ファイルをアップロード</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>実 Whisper 外部APIキー。解除: キー設定</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SO01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>即時実行ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>run-now API 無しのため列非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>API欠如</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SM01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>マルチターン</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>queued→parsing→done の状態継続</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>アップロード後</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>1. 完了までポーリングを観察</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>transcribe 状態遷移は Whisper 依存。解除: 同上</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SO01-012</t>
+          <t>SM01-012</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -13314,12 +13146,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SO01-013</t>
+          <t>SM01-013</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -13361,12 +13193,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SO01-014</t>
+          <t>SM01-014</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -13408,12 +13240,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SO01-015</t>
+          <t>SM01-015</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -13458,6 +13290,775 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SO01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SO01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SO01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SO01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /cron-schedules?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SO01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /cron-schedules?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SO01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SO01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「有効/無効トグル」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SO01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SO01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SO01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>即時実行ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>run-now API 無しのため列非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>API欠如</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SO01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SO01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SO01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SO01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14179,7 +14780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15106,587 +15707,6 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -15767,12 +15787,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -15792,7 +15812,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -15810,12 +15830,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -15857,12 +15877,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -15872,7 +15892,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -15882,7 +15902,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -15900,12 +15920,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -15915,12 +15935,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が空配列</t>
+          <t>GET /workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -15947,12 +15967,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -15962,12 +15982,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が 5xx</t>
+          <t>GET /workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -15994,12 +16014,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-006</t>
+          <t>TUC38-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -16009,7 +16029,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（現在WS内プロジェクト）</t>
+          <t>403 拒否表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -16019,7 +16039,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで プロジェクト切替 を開く</t>
+          <t>1. 権限なしで ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -16041,12 +16061,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -16056,7 +16076,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -16066,12 +16086,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -16088,12 +16108,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -16135,12 +16155,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-009</t>
+          <t>TUC38-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -16182,12 +16202,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -16229,12 +16249,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -16279,6 +16299,587 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19810,6 +20411,1018 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SB03-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. サイドバー「設定」から開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全セクション（基本情報/AI学習設定/クライアント招待/エクスポート/危険な操作）が表示</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>.audit-b03 実走</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SB03-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects/{id} の実値がフォーム初期値に入る</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>project 選択済</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を開く 2. 各欄を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>名前/クライアント名/説明/種別/ステータスが API 実値</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC1-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SB03-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト名の必須バリデーション</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 名前を空にし保存</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>「入力必須」エラーが表示され PATCH は飛ばない</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>vitest (zod min 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SB03-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>クライアント名を編集→保存→DB 反映→リロード永続</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. クライアント名変更 2. 保存 3. リロード</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /projects/{id} に client_name が載り DB 更新・再取得でも表示</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC4-5 DB突合。契約拡張 (v2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SB03-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>種別 (自社/クライアント/個人) を変更→保存→DB enum 変換</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 種別変更 2. 保存</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>契約 enum (client_project 等) → DB enum (client_work 等) にマップされ永続</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC6。v2 で新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SB03-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ステータス「下書き」が丸められず往復する</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>status=draft の project</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. draft のまま保存</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>draft のまま維持（旧実装は active へ化けた実バグ）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TC3/TC7 + pytest</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB03-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>AI 学習トグルが GET の実値で初期化される</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>ai_learning_opt_out=true</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を開く</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>トグル OFF（許可しない）。opt_out=false なら ON</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TC8/TC10。旧実装は常に OFF 表示の実バグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB03-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AI 学習トグル ON → POST /ai-learning → DB 反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. トグルをクリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>POST /projects/{id}/ai-learning {opt_out:false}、DB ai_training_optout=false、リロード後も ON</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>TC9-10 DB突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB03-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>AI 学習トグル失敗時ロールバック + エラー表示</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>API 5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. トグル操作を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>表示が元に戻り「変更に失敗しました」</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>vitest (onError)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SB03-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>エクスポート 5 ボタン (ヒアリング〜機能分解) が実 API を叩く</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 各ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>GET /outputs?project_id&amp;stage → content-url → 署名 URL を新タブで開く</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>TC11 系。旧実装は onClick 皆無の死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SB03-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>成果物 0 件の工程は明示メッセージ</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>outputs 0 件</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 要件定義をクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>「『要件定義』の成果物はまだありません。」</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SB03-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>storage 未設定 (503) を明示</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>dev 環境</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 成果物ありの工程をクリック</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>「storage が未設定です」と原因を明示（握り潰さない）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>TC11。鉄則6: 受付でなく終端を検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB03-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>削除は 2 段階確認（1 クリック目で消えない）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 「プロジェクトを削除」クリック</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>「本当に削除しますか？」+ 確定/キャンセル。確定まで DELETE 不発</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>TC13-14 DB突合。旧実装は即 DELETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB03-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>削除確定 → DELETE /projects/{id} → 一覧へ遷移</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除→確定</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>soft-delete（30日 grace）+ onDeleted で /projects へ</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>vitest。実 DELETE は監査対象を消すため fake client で検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB03-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>「招待管理を開く」→ S-L01 へ project 文脈つき遷移</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. リンククリック</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>/portal/invitations?project={id} へ遷移（意味的 URL）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>TC15。v2 で内部 URL 直リンクを是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB03-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>403 のとき拒否メッセージ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 他人の project id で開く</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>「編集する権限がありません」(role=alert)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>vitest + RLS (T-D-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SB03-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗時 inline error</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>GET 5xx</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. API 失敗で開く</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>「取得に失敗しました」(role=alert)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SB03-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない・操作できる</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開き操作</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し、種別/ステータスは 390 で縦積み、全操作可能</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>TC16-17 + 390 フルページ目視</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SB03-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>リロードでログアウトに飛ばず ?project= 文脈維持</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. F5</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>フォームが再取得され表示継続</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>TC5/TC10 のリロード経路で実証</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SB03-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト設定</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>project 未選択時は案内メッセージ</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>?project= なし</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. /projects/settings を直接開く</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトを選択すると設定を表示します。」</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>page.tsx 分岐 (vitest 対象外・実装確認) → 実機で目視</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20432,7 +22045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21275,7 +22888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21484,45 +23097,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SE01-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>チャット</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>スレッド0件時の空状態</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>スレッド0件</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. 空プロジェクトで開く</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>「スレッドがありません…」の empty state (500 にならない)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>セクションH</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH。2026-07-19 実走 (.audit-e01-fill.mjs) 空プロジェクトで empty state 表示・スクショ SE01-004-empty.png</t>
         </is>
       </c>
     </row>
@@ -22185,45 +23802,49 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>SE01-019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>チャット</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>他 WS ユーザーのスレッドが見えない (RLS)</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>別WSユーザー</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. 別アカウントで開く</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>一覧に出ない・直接 ID アクセスは 404</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>セクションG 越境 (API 層は test_chat.py で PASS)</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境。2026-07-19 実走: 新規ユーザー実サインアップ→一覧 0 件・直接 ID 404・UI 描画リークなし (SE01-019-rls.png)</t>
         </is>
       </c>
     </row>
@@ -22271,587 +23892,6 @@
       <c r="I21" s="4" t="inlineStr">
         <is>
           <t>実操作 (監査スクリプトの起動経路)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SF01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 工程ワークフロー(司令塔) を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SF01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SF01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 工程ワークフロー(司令塔) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SF01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /workflow/phases?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SF01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /workflow/phases?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SF01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（工程一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 工程ワークフロー(司令塔) を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SF01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「工程ノード/依存エッジ」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「工程ノード/依存エッジ」を目視</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>order 順ノード + 隣接エッジを描画（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SF01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SF01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SF01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SF01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>工程ワークフロー(司令塔)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -13,29 +13,30 @@
     <sheet name="SB01_プロジェクト一覧" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SB02_プロジェクトダッシュボード" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="SB03_プロジェクト設定" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SC01_AI社員 組織図" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SC02_AI社員 編集" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SE01_チャット" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SF01_工程ワークフロー(司令塔)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SF02_フェーズ管理" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="SG01_成果物ビューア" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="SH01_モックビューア" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SI01_タスクボード" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SI02_タスク詳細(6タブ)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="SI03_実行モニタ(SSE)" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="SJ01_承認インボックス" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="SK01_ナレッジエクスプローラ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="SK02_昇格レビュー" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="SL01_クライアント招待管理" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="SL02_クライアントサインイン" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="SL03_クライアントプロジェクトビュー" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="SM01_議事録アップロード" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="SO01_自動スケジュール(cron)" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="TUC36_通知センター" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="TUC37_プロフィール" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="TUC38_ワークスペース切替" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="TUC39_プロジェクト切替" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="TUC40_グローバル検索" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="SB04_プロジェクト・シークレット" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SC01_AI社員 組織図" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SC02_AI社員 編集" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SE01_チャット" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SF01_工程ワークフロー(司令塔)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SF02_フェーズ管理" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SG01_成果物ビューア" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="SH01_モックビューア" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SI01_タスクボード" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="SI02_タスク詳細(6タブ)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SI03_実行モニタ(SSE)" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="SJ01_承認インボックス" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SK01_ナレッジエクスプローラ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SK02_昇格レビュー" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SL01_クライアント招待管理" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="SL02_クライアントサインイン" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="SL03_クライアントプロジェクトビュー" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="SM01_議事録アップロード" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="SO01_自動スケジュール(cron)" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="TUC36_通知センター" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TUC37_プロフィール" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="TUC40_グローバル検索" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -662,14 +663,14 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AI社員 組織図(SC01)</t>
+          <t>プロジェクト・シークレット(SB04)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -681,14 +682,14 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AI社員 編集(SC02)</t>
+          <t>AI社員 組織図(SC01)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
@@ -700,14 +701,14 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>チャット(SE01)</t>
+          <t>AI社員 編集(SC02)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -719,14 +720,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>工程ワークフロー(司令塔)(SF01)</t>
+          <t>チャット(SE01)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
@@ -738,14 +739,14 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>フェーズ管理(SF02)</t>
+          <t>工程ワークフロー(司令塔)(SF01)</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -757,14 +758,14 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>成果物ビューア(SG01)</t>
+          <t>フェーズ管理(SF02)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -776,14 +777,14 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>モックビューア(SH01)</t>
+          <t>成果物ビューア(SG01)</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
@@ -795,14 +796,14 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>タスクボード(SI01)</t>
+          <t>モックビューア(SH01)</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0</v>
@@ -814,14 +815,14 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>タスク詳細(6タブ)(SI02)</t>
+          <t>タスクボード(SI01)</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -833,17 +834,17 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>実行モニタ(SSE)(SI03)</t>
+          <t>タスク詳細(6タブ)(SI02)</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
@@ -852,17 +853,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>承認インボックス(SJ01)</t>
+          <t>実行モニタ(SSE)(SI03)</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
@@ -871,14 +872,14 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ナレッジエクスプローラ(SK01)</t>
+          <t>承認インボックス(SJ01)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -890,14 +891,14 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>昇格レビュー(SK02)</t>
+          <t>ナレッジエクスプローラ(SK01)</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -909,14 +910,14 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>クライアント招待管理(SL01)</t>
+          <t>昇格レビュー(SK02)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>
@@ -928,14 +929,14 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>クライアントサインイン(SL02)</t>
+          <t>クライアント招待管理(SL01)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
@@ -947,14 +948,14 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>クライアントプロジェクトビュー(SL03)</t>
+          <t>クライアントサインイン(SL02)</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>0</v>
@@ -966,17 +967,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>議事録アップロード(SM01)</t>
+          <t>クライアントプロジェクトビュー(SL03)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
@@ -985,17 +986,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)(SO01)</t>
+          <t>議事録アップロード(SM01)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0</v>
@@ -1004,14 +1005,14 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>通知センター(TUC36)</t>
+          <t>自動スケジュール(cron)(SO01)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1023,14 +1024,14 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>プロフィール(TUC37)</t>
+          <t>通知センター(TUC36)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -1042,14 +1043,14 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替(TUC38)</t>
+          <t>プロフィール(TUC37)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
@@ -1061,7 +1062,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替(TUC39)</t>
+          <t>ワークスペース切替(TUC38)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1080,19 +1081,38 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索(TUC40)</t>
+          <t>プロジェクト切替(TUC39)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索(TUC40)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1102,6 +1122,1018 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SE01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>3ペイン構成が正常表示（モック S-E01-thread.html 準拠: 左260px スレッド/中央チャット/右340px コンテキスト）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済+スレッド有</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>3ペインが描画され、モックの主要領域(スレッド検索/新規スレッド/工程グルーピング/工程文脈バー/社員ヘッダー/コンポーザ/右タブ)が全て存在</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ (design-audit R2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SE01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-*/--rounded-* トークン準拠・社員カラーはモック avatar-* 準拠</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>スクショ照合済</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SE01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>スレッド一覧が実 API (GET /chat/threads?project_id) から描画</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 開いて一覧を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>実スレッドが工程グルーピング(現在→完了→横断)で表示・message_count/相対時刻付き</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SE01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>スレッド0件時の空状態</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>スレッド0件</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 空プロジェクトで開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>「スレッドがありません…」の empty state (500 にならない)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH。2026-07-19 実走 (.audit-e01-fill.mjs) 空プロジェクトで empty state 表示・スクショ SE01-004-empty.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SE01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>送信失敗時のエラーバナー(単一・dismiss可)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>LLM 未設定 or API 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. メッセージ送信</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザ直上に role=alert バナー1箇所のみ・✕で閉じる・スレッド切替でリセット</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (二重表示バグ修正済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SE01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド検索フィルタ（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>スレッド複数</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に「競合」入力</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>タイトル/社員名/最終メッセージで絞り込まれる</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SE01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>スレッド切替・新規スレッド作成（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 別スレッドをクリック 2. 新規スレッドで作成</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>メッセージが切替わる/POST /chat/threads (phase_id 任意) で作成され選択される</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>切替=実操作・作成=vitest 配線試験</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SE01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ペイン開閉トグル（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 左右トグルを各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>左ペイン/右ペインが開閉し grid が追従・aria-pressed 反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SE01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ送信 (Enter=送信 / Shift+Enter=改行 / IME 変換中は送信しない)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>スレッド選択済</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 入力して Enter</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>user バブル即時表示→SSE 応答 (LLM 無環境では誠実なエラー表示)・IME 変換確定 Enter で誤送信しない</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Enter 送信=実操作。IME は目視未 (JSDOM 契約のみ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SE01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>@メンション ピッカー（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員複数</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. @メンション をクリック 2. 社員を選択</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>実 AI 社員一覧(対話相手は除外)が出て、カーソル位置に「@名前 」が挿入される</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>実操作: textarea="この件、@ワンダ " を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SE01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナレッジ参照ピッカー（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. ナレッジ参照をクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>実ナレッジ一覧から選択で「[ナレッジ: title] 」挿入。0件時は「まだありません+自動RAGは常時有効」の誠実表示</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (0件経路)。1件以上経路は planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SE01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>死に要素ゼロ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>コンポーザに非機能ボタンが存在しない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. コンポーザの全ボタンを列挙</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>添付・/コマンドのボタンは**描画されない**(gap tracker 起票済)。表示される全ボタンが機能する</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>実操作: 添付=0個・/コマンド=0個 を機械確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SE01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>tool ロールメッセージのツールカード描画</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>tool メッセージ有</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 該当スレッドを開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>monospace ツール名ヘッダ+本文カード (モック .tool-card 準拠)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SE01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>工程文脈バー (現在の工程・Stage n/9・工程画面リンク)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. ヘッダーを確認 2. リンクをクリック</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>実 current_phase を表示し /workflow?project= へ遷移</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>表示=実操作。遷移クリックは planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SE01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>表示</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>右ペイン: 主力決定/コンテキスト/参照タブ</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>decisions 有</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各タブをクリック</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>実 /decisions の確定カード(反映先付)・F-CTX01 実測値(SSE context)・実 /knowledge 一覧</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>主力決定=実操作。コンテキスト/参照タブ切替クリックは planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SE01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>履歴</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>リロードで会話が消えない (既存メッセージロード)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>メッセージ有</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. F5</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>過去メッセージが created_at 付きで再表示</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (バグ#23 回帰)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SE01-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れない・モバイルは一覧⇄チャット切替</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く 2. モバイルで戻るボタン</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し・モバイルで戻る→一覧表示・右ペインは重ね表示トグル</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>実操作+スクショ 3幅</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SE01-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>axe 0 critical/serious・log role/aria-live/label 契約</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. axe 実行</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>違反0・role=log aria-live=polite・「メッセージを入力」label</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>vitest 契約試験 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SE01-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>他 WS ユーザーのスレッドが見えない (RLS)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>別WSユーザー</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. 別アカウントで開く</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>一覧に出ない・直接 ID アクセスは 404</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境。2026-07-19 実走: 新規ユーザー実サインアップ→一覧 0 件・直接 ID 404・UI 描画リークなし (SE01-019-rls.png)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SE01-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>?thread= URL で直接スレッドを開ける</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. /chat?thread=&lt;id&gt; を開く</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>該当スレッドが選択状態で開く</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>実操作 (監査スクリプトの起動経路)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1682,7 +2714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2404,7 +3436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3631,7 +4663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4486,7 +5518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5490,7 +6522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6670,7 +7702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7302,7 +8334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8071,7 +9103,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8642,822 +9674,6 @@
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SK02-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 昇格レビュー を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SK02-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SK02-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 昇格レビュー を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SK02-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /knowledge/promotions が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SK02-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /knowledge/promotions が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SK02-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（昇格候補）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 昇格レビュー を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SK02-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「承認」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「承認」をクリック</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SK02-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>「却下」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 「却下」をクリック</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SK02-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>承認: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 承認 を実行</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>POST 昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SK02-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>承認: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 承認 を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SK02-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>承認: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 承認 を失敗させる</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SK02-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>却下はクライアント dismiss</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 却下</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>reject API 無しのため一覧から即時除去(honest)</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>API欠如</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SK02-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SK02-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SK02-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SK02-016</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>昇格レビュー</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -10278,6 +10494,822 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SK02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 昇格レビュー を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SK02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SK02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 昇格レビュー を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SK02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /knowledge/promotions が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SK02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /knowledge/promotions が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SK02-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（昇格候補）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 昇格レビュー を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SK02-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「承認」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「承認」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>昇格処理→楽観除外（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SK02-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>「却下」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 「却下」をクリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>却下 API 無し→クライアント側 dismiss（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SK02-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>承認: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を実行</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>POST 昇格承認 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SK02-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>承認: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SK02-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>承認: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 承認 を失敗させる</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SK02-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>却下はクライアント dismiss</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 却下</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>reject API 無しのため一覧から即時除去(honest)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>API欠如</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SK02-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SK02-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SK02-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SK02-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>昇格レビュー</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11182,7 +12214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11892,7 +12924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12506,779 +13538,6 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SM01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SM01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>SM01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1. 議事録アップロード を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>transcribe 依存 (実 Whisper 外部APIキー)。解除: キー設定+実mp3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SM01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>GET /meetings/{id} が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>SM01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>GET /meetings/{id} が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>SM01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>403 拒否表示（状態ポーリング）</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 議事録アップロード を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SM01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「ファイル選択」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「ファイル選択」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>SM01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: 送信→反映</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>必須入力済</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>upload-url→PUT→POST /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>同上 (upload-url→実PUT 200 までは v4/v11 PASS 済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>SM01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>1. アップロード→transcription を失敗させる</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>SM01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>G3実副作用</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>実 storage/Whisper 副作用(BLOCKED)</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>実DB/実storage</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1. 実ファイルをアップロード</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>実 Whisper 外部APIキー。解除: キー設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>SM01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>マルチターン</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>queued→parsing→done の状態継続</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>アップロード後</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>1. 完了までポーリングを観察</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>transcribe 状態遷移は Whisper 依存。解除: 同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SM01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SM01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SM01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SM01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>議事録アップロード</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -13359,12 +13618,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>SO01-001</t>
+          <t>SM01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -13384,7 +13643,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 自動スケジュール(cron) を開く</t>
+          <t>1. 議事録アップロード を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -13402,12 +13661,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>SO01-002</t>
+          <t>SM01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -13447,198 +13706,202 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SO01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SM01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>データ取得</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>取得未完</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. 議事録アップロード を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>transcribe 依存 (実 Whisper 外部APIキー)。解除: キー設定+実mp3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SO01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SM01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>空データ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /cron-schedules?project_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GET /meetings/{id} が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. データ0件で開く</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SO01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SM01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>エラー</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /cron-schedules?project_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>GET /meetings/{id} が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. API を 500 でモックし開く</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>role=alert の inline error 表示 かつ toast 発火</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SO01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SM01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>権限</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（スケジュール一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>403 拒否表示（状態ポーリング）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>権限なしユーザ</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 議事録アップロード を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SO01-007</t>
+          <t>SM01-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13648,7 +13911,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
+          <t>「ファイル選択」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -13658,12 +13921,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「有効/無効トグル」をクリック</t>
+          <t>1. 「ファイル選択」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>署名URL発行→実PUT→登録→transcribe キュー→polling→本文表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -13678,202 +13941,202 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SO01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SM01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: 送信→反映</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>必須入力済</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>upload-url→PUT→POST /meetings→transcribe→poll→transcript-url 呼び出し→成功表示→別GET/DBに反映</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>同上 (upload-url→実PUT 200 までは v4/v11 PASS 済)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SO01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SM01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>アップロード→transcription: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. アップロード→transcription を失敗させる</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SO01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>有効トグル: API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 有効トグル を失敗させる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SM01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>G3実副作用</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>実 storage/Whisper 副作用(BLOCKED)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>実DB/実storage</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1. 実ファイルをアップロード</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>storage にオブジェクト作成・parse_result_path 生成を実API照会で確認</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>実 Whisper 外部APIキー。解除: キー設定</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SO01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>自動スケジュール(cron)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>即時実行ボタンは非表示</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 一覧確認</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>run-now API 無しのため列非表示(honest)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>API欠如</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SM01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>議事録アップロード</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>マルチターン</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>queued→parsing→done の状態継続</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>アップロード後</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>1. 完了までポーリングを観察</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>parsed_at/parse_error まで状態が継続遷移し本文取得</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>transcribe 状態遷移は Whisper 依存。解除: 同上</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SO01-012</t>
+          <t>SM01-012</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -13915,12 +14178,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>SO01-013</t>
+          <t>SM01-013</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -13962,12 +14225,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SO01-014</t>
+          <t>SM01-014</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -14009,12 +14272,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>SO01-015</t>
+          <t>SM01-015</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)</t>
+          <t>議事録アップロード</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -14059,6 +14322,775 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SO01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SO01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SO01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 自動スケジュール(cron) を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SO01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /cron-schedules?project_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SO01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /cron-schedules?project_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SO01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（スケジュール一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 自動スケジュール(cron) を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SO01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「有効/無効トグル」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「有効/無効トグル」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>PATCH enabled(楽観トグル)（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SO01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /cron-schedules/{id} 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SO01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SO01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有効トグル: API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 有効トグル を失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SO01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>即時実行ボタンは非表示</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧確認</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>run-now API 無しのため列非表示(honest)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>API欠如</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SO01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SO01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SO01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SO01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>自動スケジュール(cron)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14780,7 +15812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15707,587 +16739,6 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -16368,12 +16819,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -16393,7 +16844,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -16411,12 +16862,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -16458,12 +16909,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -16473,7 +16924,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -16483,7 +16934,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -16501,12 +16952,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -16516,12 +16967,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が空配列</t>
+          <t>GET /workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -16548,12 +16999,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -16563,12 +17014,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が 5xx</t>
+          <t>GET /workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -16595,12 +17046,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-006</t>
+          <t>TUC38-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -16610,7 +17061,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（現在WS内プロジェクト）</t>
+          <t>403 拒否表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -16620,7 +17071,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで プロジェクト切替 を開く</t>
+          <t>1. 権限なしで ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -16642,12 +17093,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -16657,7 +17108,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -16667,12 +17118,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -16689,12 +17140,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -16736,12 +17187,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-009</t>
+          <t>TUC38-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -16783,12 +17234,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -16830,12 +17281,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -16885,7 +17336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16949,12 +17400,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC40-001</t>
+          <t>TUC39-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -16974,7 +17425,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. グローバル検索 を開く</t>
+          <t>1. プロジェクト切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -16992,12 +17443,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC40-002</t>
+          <t>TUC39-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -17039,12 +17490,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC40-003</t>
+          <t>TUC39-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -17054,7 +17505,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（横断検索）</t>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -17064,7 +17515,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. グローバル検索 を開き取得完了前を観察</t>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -17082,12 +17533,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC40-004</t>
+          <t>TUC39-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -17097,12 +17548,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（横断検索）</t>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /search?q=&amp;kind= が空配列</t>
+          <t>GET /projects?workspace_id が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -17129,12 +17580,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC40-005</t>
+          <t>TUC39-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -17144,12 +17595,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（横断検索）</t>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /search?q=&amp;kind= が 5xx</t>
+          <t>GET /projects?workspace_id が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -17176,12 +17627,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC40-006</t>
+          <t>TUC39-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -17191,7 +17642,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（横断検索）</t>
+          <t>403 拒否表示（現在WS内プロジェクト）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -17201,7 +17652,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで グローバル検索 を開く</t>
+          <t>1. 権限なしで プロジェクト切替 を開く</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -17223,22 +17674,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC40-007</t>
+          <t>TUC39-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>入力フォーム</t>
+          <t>インタラクション</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>初期値/placeholder（キーワード）</t>
+          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -17248,12 +17699,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. フォームを開く</t>
+          <t>1. 「Project picker」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>キーワード の初期値/placeholder が正しい</t>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -17261,27 +17712,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC40-008</t>
+          <t>TUC39-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>バリデーション</t>
+          <t>a11y</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>キーワード: 必須(空で未検索)</t>
+          <t>axe scan で 0 critical/serious</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -17291,12 +17746,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. キーワード に不正値/未入力を入れる</t>
+          <t>1. axe を実行</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -17304,27 +17759,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC40-009</t>
+          <t>TUC39-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>レスポンシブ</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（死にボタン検査）</t>
+          <t>320/768/1024/1440 で崩れない</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -17334,12 +17793,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
+          <t>1. 各幅で開く</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -17349,44 +17808,44 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>死にボタン</t>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TUC40-010</t>
+          <t>TUC39-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>状態永続</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>「検索入力」を操作すると動作する（死にボタン検査）</t>
+          <t>F5 リロードでログアウトに飛ばない</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ログイン済</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. 「検索入力」を入力(debounce)</t>
+          <t>1. 画面で F5</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>GET /search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -17396,29 +17855,29 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>死にボタン</t>
+          <t>セクションG G4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TUC40-011</t>
+          <t>TUC39-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>グローバル検索</t>
+          <t>プロジェクト切替</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R-T08</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>RLS で可視性担保</t>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -17428,12 +17887,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. 検索実行</t>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>RLS 内のみヒット(越境自動除外)</t>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -17442,194 +17901,6 @@
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -18538,6 +18809,767 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（横断検索）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（横断検索）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /search?q=&amp;kind= が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（横断検索）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /search?q=&amp;kind= が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（横断検索）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで グローバル検索 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（キーワード）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>キーワード の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>キーワード: 必須(空で未検索)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. キーワード に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>「検索入力」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 「検索入力」を入力(debounce)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>GET /search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>R-T08</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>RLS で可視性担保</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>RLS 内のみヒット(越境自動除外)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -21423,6 +22455,1018 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SB04-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>主要領域 (注意書き/新規追加/一覧) がモック準拠で表示</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>project 選択済</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. サイドバー「シークレット」から開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>secure-note (amber)・フォーム・一覧テーブルが揃う</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>TC1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SB04-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>フォームから作成 → 一覧反映</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 名称/種別/値を入力 2. 暗号化して保存</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>POST 201 → 一覧に新行 (別 GET 再取得)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SB04-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>DB は暗号化保存・平文を含まない</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>作成直後</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. psql で encrypted_value を確認</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Fernet 暗号文のみ・平文部分文字列なし・last4 記録</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TC3 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SB04-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>一覧の値はマスク (••••••••last4)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>平文は出ない</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SB04-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>作成者列に実ユーザー名</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>created_by → users.display_name (契約拡張 v2)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC5。旧実装は列ごと欠落</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SB04-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>作成日が YYYY-MM-DD (生 ISO 露出なし)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>人間可読の日付 (鉄則5)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TC6。旧実装は生 ISO を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SB04-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「表示」→ 復号平文が一時表示</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>reveal API → 平文 + コピー/隠す</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TC7/TC9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SB04-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>reveal が監査ログに記録される</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示 2. psql audit_logs</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>action=credential.reveal が +1</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>TC8 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SB04-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「隠す」でマスクへ復帰 (平文を保持しない)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>表示中</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 隠すをクリック</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>マスク表示へ戻る</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SB04-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>reveal 失敗時に明示エラー (握り潰さない)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>API 5xx/403</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>role=alert「復号に失敗しました…」</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>vitest。旧実装は無言で終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SB04-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>他ユーザーは一覧不可・reveal 404 (RLS)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>別 WS ユーザー</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 実サインアップした別ユーザーで API</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>一覧 0 件・reveal 404</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>TC11-12 実ユーザーで越境=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SB04-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>削除は 2 段階確認</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. ゴミ箱 → 削除する</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1 クリック目は確認のみ。確定で DELETE</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>TC13。旧実装は即削除 (機密で確認なしは危険)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SB04-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>削除確定 → 一覧から消え DB soft-delete</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除確定 2. psql</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>deleted_at セット・一覧再取得で消滅</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>TC14 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SB04-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>名称/値の必須チェック</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 空のまま保存</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>「名前と値は必須です。」・POST 不発</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SB04-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>既定種別=トークン (モック準拠)・成功後は全欄クリア</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 送信成功後を目視</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>値を画面に残さない (機密)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>vitest。旧実装の既定は「その他」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SB04-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>保存失敗時に role=alert</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>POST 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>エラーメッセージ表示・入力は保持</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SB04-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>0 件</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 空の project で開く</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>「まだ何も保管されていません。」</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>vitest + 実機 (削除後の 390 スクショ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SB04-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れず操作可能</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開き入力</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>body 横スクロール無し (表は自前スクロール)・フォーム操作可</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>TC15-16 + 390 目視</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SB04-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>project 未指定は明示メッセージ</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>?project= なし</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. /projects/vault 直接</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトが指定されていません。」</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>実機確認済 (.b04-edge: メッセージ表示を実走)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SB04-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>シークレット</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>401 で signin へ誘導</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>未ログイン</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. cookie なしで開く</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>/signin?redirect=... へ</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>実機確認済 (.b04-edge: cookie なし→ /signin 遷移を実走)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -22045,7 +24089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22886,1016 +24930,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>SE01-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>3ペイン構成が正常表示（モック S-E01-thread.html 準拠: 左260px スレッド/中央チャット/右340px コンテキスト）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済+スレッド有</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. /chat を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>3ペインが描画され、モックの主要領域(スレッド検索/新規スレッド/工程グルーピング/工程文脈バー/社員ヘッダー/コンポーザ/右タブ)が全て存在</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>実操作+スクショ (design-audit R2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>SE01-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-*/--rounded-* トークン準拠・社員カラーはモック avatar-* 準拠</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>スクショ照合済</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>SE01-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>スレッド一覧が実 API (GET /chat/threads?project_id) から描画</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. 開いて一覧を確認</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>実スレッドが工程グルーピング(現在→完了→横断)で表示・message_count/相対時刻付き</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>実操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SE01-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>スレッド0件時の空状態</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>スレッド0件</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. 空プロジェクトで開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>「スレッドがありません…」の empty state (500 にならない)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH。2026-07-19 実走 (.audit-e01-fill.mjs) 空プロジェクトで empty state 表示・スクショ SE01-004-empty.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>SE01-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>送信失敗時のエラーバナー(単一・dismiss可)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>LLM 未設定 or API 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. メッセージ送信</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>コンポーザ直上に role=alert バナー1箇所のみ・✕で閉じる・スレッド切替でリセット</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>実操作 (二重表示バグ修正済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SE01-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>スレッド検索フィルタ（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>スレッド複数</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 検索欄に「競合」入力</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>タイトル/社員名/最終メッセージで絞り込まれる</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>実操作+スクショ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SE01-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>スレッド切替・新規スレッド作成（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 別スレッドをクリック 2. 新規スレッドで作成</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>メッセージが切替わる/POST /chat/threads (phase_id 任意) で作成され選択される</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>切替=実操作・作成=vitest 配線試験</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SE01-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ペイン開閉トグル（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 左右トグルを各クリック</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>左ペイン/右ペインが開閉し grid が追従・aria-pressed 反映</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>実操作+スクショ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>SE01-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>メッセージ送信 (Enter=送信 / Shift+Enter=改行 / IME 変換中は送信しない)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>スレッド選択済</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 入力して Enter</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>user バブル即時表示→SSE 応答 (LLM 無環境では誠実なエラー表示)・IME 変換確定 Enter で誤送信しない</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Enter 送信=実操作。IME は目視未 (JSDOM 契約のみ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SE01-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>@メンション ピッカー（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>AI 社員複数</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. @メンション をクリック 2. 社員を選択</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>実 AI 社員一覧(対話相手は除外)が出て、カーソル位置に「@名前 」が挿入される</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>実操作: textarea="この件、@ワンダ " を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>SE01-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナレッジ参照ピッカー（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. ナレッジ参照をクリック</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>実ナレッジ一覧から選択で「[ナレッジ: title] 」挿入。0件時は「まだありません+自動RAGは常時有効」の誠実表示</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>実操作 (0件経路)。1件以上経路は planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SE01-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>死に要素ゼロ</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>コンポーザに非機能ボタンが存在しない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. コンポーザの全ボタンを列挙</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>添付・/コマンドのボタンは**描画されない**(gap tracker 起票済)。表示される全ボタンが機能する</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>実操作: 添付=0個・/コマンド=0個 を機械確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>SE01-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>tool ロールメッセージのツールカード描画</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>tool メッセージ有</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 該当スレッドを開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>monospace ツール名ヘッダ+本文カード (モック .tool-card 準拠)</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>実操作+スクショ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SE01-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>工程文脈バー (現在の工程・Stage n/9・工程画面リンク)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. ヘッダーを確認 2. リンクをクリック</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>実 current_phase を表示し /workflow?project= へ遷移</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>表示=実操作。遷移クリックは planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>SE01-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>表示</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>右ペイン: 主力決定/コンテキスト/参照タブ</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>decisions 有</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 各タブをクリック</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>実 /decisions の確定カード(反映先付)・F-CTX01 実測値(SSE context)・実 /knowledge 一覧</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>主力決定=実操作。コンテキスト/参照タブ切替クリックは planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>SE01-016</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>履歴</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>リロードで会話が消えない (既存メッセージロード)</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>メッセージ有</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. F5</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>過去メッセージが created_at 付きで再表示</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>実操作 (バグ#23 回帰)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>SE01-017</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>390/768/1440 で崩れない・モバイルは一覧⇄チャット切替</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く 2. モバイルで戻るボタン</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール無し・モバイルで戻る→一覧表示・右ペインは重ね表示トグル</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>実操作+スクショ 3幅</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SE01-018</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>axe 0 critical/serious・log role/aria-live/label 契約</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1. axe 実行</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>違反0・role=log aria-live=polite・「メッセージを入力」label</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>vitest 契約試験 green</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>SE01-019</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>他 WS ユーザーのスレッドが見えない (RLS)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>別WSユーザー</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1. 別アカウントで開く</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>一覧に出ない・直接 ID アクセスは 404</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境。2026-07-19 実走: 新規ユーザー実サインアップ→一覧 0 件・直接 ID 404・UI 描画リークなし (SE01-019-rls.png)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>SE01-020</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>チャット</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>?thread= URL で直接スレッドを開ける</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>1. /chat?thread=&lt;id&gt; を開く</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>該当スレッドが選択状態で開く</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>実操作 (監査スクリプトの起動経路)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -31,12 +31,13 @@
     <sheet name="SL02_クライアントサインイン" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="SL03_クライアントプロジェクトビュー" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="SM01_議事録アップロード" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="SO01_自動スケジュール(cron)" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="TUC36_通知センター" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="TUC37_プロフィール" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="TUC38_ワークスペース切替" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="TUC39_プロジェクト切替" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="TUC40_グローバル検索" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="SN01_商談ドラフト" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="SO01_自動スケジュール(cron)" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TUC36_通知センター" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TUC37_プロフィール" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="TUC40_グローバル検索" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1005,14 +1006,14 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>自動スケジュール(cron)(SO01)</t>
+          <t>商談ドラフト(SN01)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1024,14 +1025,14 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>通知センター(TUC36)</t>
+          <t>自動スケジュール(cron)(SO01)</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -1043,14 +1044,14 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>プロフィール(TUC37)</t>
+          <t>通知センター(TUC36)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
@@ -1062,14 +1063,14 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替(TUC38)</t>
+          <t>プロフィール(TUC37)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -1081,7 +1082,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替(TUC39)</t>
+          <t>ワークスペース切替(TUC38)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -1100,19 +1101,38 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索(TUC40)</t>
+          <t>プロジェクト切替(TUC39)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索(TUC40)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14327,6 +14347,830 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SN01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ナビ「営業ドラフト」から UI 到達できる</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>project 選択済</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. ダッシュボード → サイドバー営業ドラフト</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>/sales?project= に遷移し描画</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>TC1。**監査前は導線ゼロの到達不能画面** (S-O01 と同型)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SN01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>種別タブ (提案書/見積書) が実タブとして切替わる</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 見積書タブをクリック</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>aria-selected 遷移・一覧/フォーム見出しが追従</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC2/TC12。旧実装は 5 タブ全てクリック不能の死にタブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SN01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>タブ件数バッジが実データ</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>保存済みあり</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. タブを目視</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>GET /sales-docs の実件数</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>vitest。旧実装は v3/v2/draft の虚偽バッジ (前ラウンドで撤去済) → 実件数に</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SN01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>フォームから作成 → POST /sales-docs → プレビュー表示</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 顧客名/案件/概要 → ドラフト生成</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>doc_type=タブ追従で保存・article に本文</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC3 + vitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SN01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>作成が DB (workflow_outputs stage=proposal/estimate) に永続</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. psql 突合</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>stage/version が記録される</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC3/TC5 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SN01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>保存済みドキュメント一覧 (版数 vN + 日付)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>保存済みあり</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. サイドバーを目視</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>v1 等の版数と YYYY-MM-DD 表示</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TC4。**旧実装は一覧が無くリロードで全消失**</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SN01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>リロード後も一覧から開き直せる</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>保存済みあり</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. F5 → 一覧クリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>本文がプレビューに出る</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TC7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SN01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>編集 → PATCH /sales-docs/{id} → DB 反映</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ドキュメント選択中</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 編集 → 本文変更 → 保存</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>summary が DB 更新・表示反映</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>TC6 DB 突合 + vitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SN01-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>削除は 2 段階確認 → DB 論理削除</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. ゴミ箱 → 削除する</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>1 クリック目は確認のみ。確定で deleted_at</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>TC9-10 DB 突合 + vitest</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SN01-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>「修正依頼」がチャットへの実リンク</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. href を検証</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>/chat?project={id}</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>TC8。旧実装は disabled placeholder (Rule 10 違反)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SN01-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>PDF/送信/送信履歴/参照ナレッジは未描画 (honest)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>API 不在機能の偽装 UI が無い</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>GAP-018。disabled placeholder を全廃</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SN01-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>必須 (顧客名/案件) + 概要 10 文字未満を拒否</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 空/短文で生成</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示・POST 不発</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>vitest (zod)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SN01-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>一覧取得失敗時に role=alert</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>GET 5xx</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 失敗させる</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>「一覧の取得に失敗しました。」</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>コンポーネント分岐 + vitest 経路</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SN01-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>0 件時「まだドキュメントがありません。」</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0 件</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 空タブを目視</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>空状態表示 (500 にならない)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>実機 (見積タブ 0 件で目視)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SN01-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>390/768/1440 で崩れず操作可能</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開きタブ操作</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール無し・タブ/フォーム操作可</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>TC11-12 + 390 目視</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SN01-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>商談ドラフト</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>project 未選択時は案内メッセージ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>?project= なし</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. /sales 直接</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>「プロジェクトを選択すると…」</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>page.tsx 分岐 (S-B03/B04 と同型・実機確認済パターン)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15090,7 +15934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15812,7 +16656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16739,587 +17583,6 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /workspaces が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -17400,12 +17663,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>TUC38-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -17425,7 +17688,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -17443,12 +17706,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>TUC38-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -17490,12 +17753,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>TUC38-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -17505,7 +17768,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -17515,7 +17778,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -17533,12 +17796,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>TUC38-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -17548,12 +17811,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が空配列</t>
+          <t>GET /workspaces が空配列</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -17580,12 +17843,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>TUC38-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -17595,12 +17858,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が 5xx</t>
+          <t>GET /workspaces が 5xx</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -17627,12 +17890,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-006</t>
+          <t>TUC38-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -17642,7 +17905,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（現在WS内プロジェクト）</t>
+          <t>403 拒否表示（所属 WS 一覧）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -17652,7 +17915,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで プロジェクト切替 を開く</t>
+          <t>1. 権限なしで ワークスペース切替 を開く</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -17674,12 +17937,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>TUC38-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -17689,7 +17952,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -17699,12 +17962,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 「WS picker」を選択</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -17721,12 +17984,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>TUC38-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -17768,12 +18031,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-009</t>
+          <t>TUC38-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -17815,12 +18078,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>TUC38-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -17862,12 +18125,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>TUC38-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>ワークスペース切替</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -18815,6 +19078,587 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -33,11 +33,15 @@
     <sheet name="SM01_議事録アップロード" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="SN01_商談ドラフト" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="SO01_自動スケジュール(cron)" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="TUC36_通知センター" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="TUC37_プロフィール" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="TUC38_ワークスペース切替" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="TUC39_プロジェクト切替" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="TUC40_グローバル検索" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="SPUB01_利用規約" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="SPUB02_プライバシーポリシー" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="SPUB03_特商法表記" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="SPUB04_個人データ削除要求" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="TUC36_通知センター" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="TUC37_プロフィール" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="TUC40_グローバル検索" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1044,14 +1048,14 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>通知センター(TUC36)</t>
+          <t>利用規約(SPUB01)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
@@ -1063,14 +1067,14 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>プロフィール(TUC37)</t>
+          <t>プライバシーポリシー(SPUB02)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -1082,14 +1086,14 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替(TUC38)</t>
+          <t>特商法表記(SPUB03)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0</v>
@@ -1101,7 +1105,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替(TUC39)</t>
+          <t>個人データ削除要求(SPUB04)</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -1120,19 +1124,95 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索(TUC40)</t>
+          <t>通知センター(TUC36)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>プロフィール(TUC37)</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ワークスペース切替(TUC38)</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>プロジェクト切替(TUC39)</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索(TUC40)</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15940,7 +16020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16004,12 +16084,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC36-001</t>
+          <t>SPUB01-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -16019,22 +16099,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証で /terms が開ける (公開)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. 通知センター を開く</t>
+          <t>1. cookie なしで /terms</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>200・本文描画</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -16042,27 +16122,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実走</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC36-002</t>
+          <t>SPUB01-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>本文が正本 (GET /public/legal-documents) と一致</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -16072,12 +16156,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. API の body_md の一文が画面に出るか</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>DB 正本の文言が描画される</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -16087,44 +16171,44 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+          <t>**旧実装はハードコード縮約版で正本と乖離**</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC36-003</t>
+          <t>SPUB01-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（承認待ち集約）</t>
+          <t>版数・最終更新が実データ</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. 通知センター を開き取得完了前を観察</t>
+          <t>1. メタ行を目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>version / effective_date を表示</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -16132,42 +16216,46 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実走 (2026-05-25)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC36-004</t>
+          <t>SPUB01-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（承認待ち集約）</t>
+          <t>タイトルの二重見出しが無い</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /approval-inbox が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. h1/h2 を数える</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+          <t>見出し 1 個のみ</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -16177,44 +16265,44 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>セクションH</t>
+          <t>v2 実走で検出→修正 (body_md 先頭 H1 除去)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC36-005</t>
+          <t>SPUB01-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（承認待ち集約）</t>
+          <t>公開ヘッダーのナビ (規約/プライバシー/特商法) が遷移</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /approval-inbox が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を 500 でモックし開く</t>
+          <t>1. 各リンクをクリック</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
+          <t>相互に遷移できる</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -16224,44 +16312,44 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>UNWANTED critical</t>
+          <t>モックの pub-header を新設</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC36-006</t>
+          <t>SPUB01-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>権限</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（承認待ち集約）</t>
+          <t>API 失敗時に明示エラー</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>権限なしユーザ</t>
+          <t>GET 5xx</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで 通知センター を開く</t>
+          <t>1. 失敗させる</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+          <t>role=alert「文書の取得に失敗しました…」</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -16271,29 +16359,29 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>セクションG 越境</t>
+          <t>vitest (LegalDocArticle 分岐)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC36-007</t>
+          <t>SPUB01-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>通知センター</t>
+          <t>利用規約</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>レスポンシブ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「既読」を操作すると動作する（死にボタン検査）</t>
+          <t>390px で横スクロールなし</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -16303,12 +16391,12 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「既読」をクリック</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>localStorage に記録→未読数減・未読フィルタ連動（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -16318,336 +16406,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>「すべて/未読のみ タブ」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. 「すべて/未読のみ タブ」を各クリック</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>フィルタ切替（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>既読(localStorage): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 既読(localStorage) を実行</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>localStorage 更新 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-012</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>永続既読/承認以外の種別は別migration</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 既読挙動</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>専用テーブル(R-T08致命級)が無く localStorage 管理(MVP)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>★致命級migrationは別タスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-013</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-014</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-015</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TUC36-016</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>通知センター</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
+          <t>実走 + 目視</t>
         </is>
       </c>
     </row>
@@ -16662,7 +16421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16726,12 +16485,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC37-001</t>
+          <t>SPUB02-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロフィール</t>
+          <t>プライバシーポリシー</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -16741,22 +16500,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証で /privacy が開ける</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロフィール を開く</t>
+          <t>1. cookie なしで開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>200・本文描画</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -16764,27 +16523,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実走</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC37-002</t>
+          <t>SPUB02-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロフィール</t>
+          <t>プライバシーポリシー</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>本文が正本 (privacy_policy) と一致</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -16794,12 +16557,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. API body_md の一文を照合</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>DB 正本を描画</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -16809,44 +16572,44 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+          <t>旧実装はハードコード縮約版</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC37-003</t>
+          <t>SPUB02-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロフィール</t>
+          <t>プライバシーポリシー</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（自己プロフィール）</t>
+          <t>版数・最終更新・見出し非重複</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロフィール を開き取得完了前を観察</t>
+          <t>1. メタ/見出し目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>version 表示・見出し 1 個</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -16854,42 +16617,46 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実走</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC37-004</t>
+          <t>SPUB02-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロフィール</t>
+          <t>プライバシーポリシー</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（自己プロフィール）</t>
+          <t>公開ヘッダーナビで相互遷移</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /me が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. リンク巡回</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+          <t>/terms ↔ /privacy ↔ /tokushoho</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -16899,44 +16666,44 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>セクションH</t>
+          <t>実走</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC37-005</t>
+          <t>SPUB02-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロフィール</t>
+          <t>プライバシーポリシー</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>レスポンシブ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（自己プロフィール）</t>
+          <t>390px 横スクロールなし</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /me が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を 500 でモックし開く</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -16946,645 +16713,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（自己プロフィール）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで プロフィール を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（display_name）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>display_name の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>display_name: 必須/最大100</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. display_name に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（email）</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>email の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>email: readonly</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. email に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>「保存」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 「保存」をクリック</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /me(楽観)→保存表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>表示名保存(PATCH): 成功で即時反映</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>対象が存在</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名保存(PATCH) を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>PATCH /me 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>楽観更新</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>表示名保存(PATCH): 失敗でロールバック</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>サーバ 4xx/5xx</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名保存(PATCH) を実行しAPIが失敗</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>楽観反映が元に戻り、inline error + toast を表示</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>EVENT-DRIVEN/rollback</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>表示名保存(PATCH): API 失敗時 inline error + toast</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>接続失敗/レート</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 表示名保存(PATCH) を失敗させる</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>role=alert + toast、状態は不整合にならない</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>受容差分</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>email は readonly</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. email 欄を確認</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Auth 紐付けのため変更不可(readonly)</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-016</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-017</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-018</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>TUC37-019</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>プロフィール</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
+          <t>実走 + 目視</t>
         </is>
       </c>
     </row>
@@ -17599,7 +16728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17663,12 +16792,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC38-001</t>
+          <t>SPUB03-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替</t>
+          <t>特商法表記</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -17678,22 +16807,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証で /tokushoho が開ける</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. ワークスペース切替 を開く</t>
+          <t>1. cookie なしで開く</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>200・本文描画</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -17701,27 +16830,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実走</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC38-002</t>
+          <t>SPUB03-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替</t>
+          <t>特商法表記</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>本文が正本 (tokushoho) と一致</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -17731,12 +16864,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. API body_md の項目値を照合</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>DB 正本 (販売事業者/連絡先等) を描画</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -17746,44 +16879,44 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+          <t>**旧実装は正本と異なる事業者名/連絡先を表示** (株式会社 Atelier / info@example.com)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC38-003</t>
+          <t>SPUB03-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替</t>
+          <t>特商法表記</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（所属 WS 一覧）</t>
+          <t>版数・最終更新・見出し非重複</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
+          <t>1. メタ/見出し目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>version 表示・見出し 1 個</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -17791,42 +16924,46 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実走 (重複を v2 で検出→修正)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC38-004</t>
+          <t>SPUB03-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替</t>
+          <t>特商法表記</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（所属 WS 一覧）</t>
+          <t>公開ヘッダーナビで相互遷移</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /workspaces が空配列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. リンク巡回</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+          <t>相互遷移</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -17836,44 +16973,44 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>セクションH</t>
+          <t>実走</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC38-005</t>
+          <t>SPUB03-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ワークスペース切替</t>
+          <t>特商法表記</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>レスポンシブ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
+          <t>390px 横スクロールなし</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /workspaces が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を 500 でモックし開く</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -17883,289 +17020,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（所属 WS 一覧）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで ワークスペース切替 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「WS picker」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC38-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ワークスペース切替</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
+          <t>実走 + 目視</t>
         </is>
       </c>
     </row>
@@ -19142,37 +17997,37 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>TUC39-001</t>
+          <t>SPUB04-001</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>画面表示</t>
+          <t>権限</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+          <t>未認証はサインイン誘導</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>未ログイン</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開く</t>
+          <t>1. cookie なしで /data-deletion</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+          <t>「サインインして続ける」→ /signin?redirect=/data-deletion</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -19180,27 +18035,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実走。API は認証必須 (本人特定)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>TUC39-002</t>
+          <t>SPUB04-002</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>視覚忠実度</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
+          <t>削除内容チェックリスト + 残存データ説明 (モック準拠)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -19210,12 +18069,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1. 画面を目視</t>
+          <t>1. danger カード目視</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+          <t>6 項目 + 匿名化説明</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -19225,44 +18084,44 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+          <t>実走。旧実装はカード自体なし</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TUC39-003</t>
+          <t>SPUB04-003</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>データ取得</t>
+          <t>画面表示</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+          <t>削除スケジュールカード</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>取得未完</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+          <t>1. 目視</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+          <t>当日/30日後/キャンセル可の 3 行</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -19270,42 +18129,46 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>実走。旧実装なし</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TUC39-004</t>
+          <t>SPUB04-004</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>空データ</t>
+          <t>入力フォーム</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+          <t>ログイン中メールが表示専用 (disabled)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が空配列</t>
+          <t>ログイン済</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>1. データ0件で開く</t>
+          <t>1. email 欄を確認</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+          <t>実メールを表示・編集不可</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -19315,44 +18178,44 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>セクションH</t>
+          <t>実走。旧実装はメール 2 回手入力 (API は JWT で本人特定するため無意味だった)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>TUC39-005</t>
+          <t>SPUB04-005</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>エラー</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+          <t>「削除する」タイプ確認が必須</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>GET /projects?workspace_id が 5xx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1. API を 500 でモックし開く</t>
+          <t>1. 未入力/誤入力で申請</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
+          <t>「「削除する」と入力してください」・POST 不発</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -19362,44 +18225,44 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>UNWANTED critical</t>
+          <t>実走 + vitest。モック準拠の確認方式に是正</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>TUC39-006</t>
+          <t>SPUB04-006</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>権限</t>
+          <t>バリデーション</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>403 拒否表示（現在WS内プロジェクト）</t>
+          <t>同意チェック必須・理由は任意</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>権限なしユーザ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>1. 権限なしで プロジェクト切替 を開く</t>
+          <t>1. 同意なしで申請</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+          <t>エラー・POST 不発</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -19409,44 +18272,44 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>セクションG 越境</t>
+          <t>vitest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>TUC39-007</t>
+          <t>SPUB04-007</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>インタラクション</t>
+          <t>登録・編集</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+          <t>実申請 → POST /public/data-deletion-requests → 受付番号表示</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ログイン済</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1. 「Project picker」を選択</t>
+          <t>1. 正しく入力し申請</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+          <t>201 → 受付番号 + 30 日案内</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -19456,44 +18319,44 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>死にボタン</t>
+          <t>実走。**旧実装は onSubmit が no-op の偽フォーム**</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TUC39-008</t>
+          <t>SPUB04-008</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>a11y</t>
+          <t>整合性</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>axe scan で 0 critical/serious</t>
+          <t>申請が audit_logs に記録される</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>申請直後</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1. axe を実行</t>
+          <t>1. psql 突合</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
+          <t>action=data_deletion.request が actor 本人で +1</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -19503,29 +18366,29 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>vitest-axe 実測済(該当時)</t>
+          <t>実走 DB 突合 (F-LEGAL-002)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>TUC39-009</t>
+          <t>SPUB04-009</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>レスポンシブ</t>
+          <t>到達性</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>320/768/1024/1440 で崩れない</t>
+          <t>キャンセル/戻りリンクが /privacy へ</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -19535,12 +18398,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1. 各幅で開く</t>
+          <t>1. リンク確認</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
+          <t>href=/privacy</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -19550,44 +18413,44 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+          <t>vitest + 実走 (pub-header 戻りリンク)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>TUC39-010</t>
+          <t>SPUB04-010</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>状態永続</t>
+          <t>エラー</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
+          <t>送信失敗時に明示エラー</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ログイン済</t>
+          <t>POST 5xx</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>1. 画面で F5</t>
+          <t>1. 失敗させる</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+          <t>role=alert「送信に失敗しました…」</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -19597,29 +18460,29 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>セクションG G4</t>
+          <t>コンテナ分岐 (vitest 対象経路)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>TUC39-011</t>
+          <t>SPUB04-011</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>プロジェクト切替</t>
+          <t>データ削除要求</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>到達性</t>
+          <t>レスポンシブ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+          <t>390px 横スクロールなし</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -19629,12 +18492,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+          <t>1. 390 で開く</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+          <t>崩れなし</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -19644,7 +18507,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
+          <t>実走 + 目視</t>
         </is>
       </c>
     </row>
@@ -19654,6 +18517,2827 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 通知センター を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 通知センター を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /approval-inbox が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /approval-inbox が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（承認待ち集約）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで 通知センター を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「既読」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「既読」をクリック</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage に記録→未読数減・未読フィルタ連動（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>「すべて/未読のみ タブ」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 「すべて/未読のみ タブ」を各クリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>フィルタ切替（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>既読(localStorage): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 既読(localStorage) を実行</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>localStorage 更新 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-012</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>永続既読/承認以外の種別は別migration</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 既読挙動</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>専用テーブル(R-T08致命級)が無く localStorage 管理(MVP)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>★致命級migrationは別タスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-013</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-014</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-015</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TUC36-016</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>通知センター</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロフィール を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロフィール を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /me が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /me が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（自己プロフィール）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで プロフィール を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（display_name）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>display_name の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>display_name: 必須/最大100</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. display_name に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（email）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>email の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>email: readonly</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. email に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>「保存」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 「保存」をクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /me(楽観)→保存表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>表示名保存(PATCH): 成功で即時反映</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>対象が存在</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名保存(PATCH) を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /me 呼び出し前にUIへ楽観反映→成功で確定（別GET再取得で反映）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>楽観更新</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>表示名保存(PATCH): 失敗でロールバック</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>サーバ 4xx/5xx</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名保存(PATCH) を実行しAPIが失敗</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>楽観反映が元に戻り、inline error + toast を表示</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>EVENT-DRIVEN/rollback</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>表示名保存(PATCH): API 失敗時 inline error + toast</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>接続失敗/レート</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 表示名保存(PATCH) を失敗させる</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>role=alert + toast、状態は不整合にならない</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>email は readonly</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. email 欄を確認</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Auth 紐付けのため変更不可(readonly)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TUC37-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>プロフィール</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. ワークスペース切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（所属 WS 一覧）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. ワークスペース切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（所属 WS 一覧）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /workspaces が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（所属 WS 一覧）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /workspaces が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（所属 WS 一覧）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで ワークスペース切替 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「WS picker」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「WS picker」を選択</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_workspace) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC38-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ワークスペース切替</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
+++ b/apps/web/.qa/テスト仕様書_エンジニア版.xlsx
@@ -37,11 +37,17 @@
     <sheet name="SPUB02_プライバシーポリシー" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="SPUB03_特商法表記" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="SPUB04_個人データ削除要求" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="TUC36_通知センター" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="TUC37_プロフィール" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="TUC38_ワークスペース切替" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="TUC39_プロジェクト切替" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="TUC40_グローバル検索" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="ST01_運営ダッシュボード" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ST02_スキル管理" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ST03_AI 社員テンプレート" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="ST04_ユーザー管理" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="ST05_監査ログ" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="ST06_運営デフォルト・ナレッジ" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="TUC36_通知センター" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="TUC37_プロフィール" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="TUC38_ワークスペース切替" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="TUC39_プロジェクト切替" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="TUC40_グローバル検索" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1124,14 +1130,14 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>通知センター(TUC36)</t>
+          <t>運営ダッシュボード(ST01)</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1143,14 +1149,14 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>プロフィール(TUC37)</t>
+          <t>スキル管理(ST02)</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -1162,14 +1168,14 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ワークスペース切替(TUC38)</t>
+          <t>AI 社員テンプレート(ST03)</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -1181,14 +1187,14 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>プロジェクト切替(TUC39)</t>
+          <t>ユーザー管理(ST04)</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -1200,19 +1206,133 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>グローバル検索(TUC40)</t>
+          <t>監査ログ(ST05)</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>運営デフォルト・ナレッジ(ST06)</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>通知センター(TUC36)</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>プロフィール(TUC37)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ワークスペース切替(TUC38)</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>プロジェクト切替(TUC39)</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>グローバル検索(TUC40)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18522,6 +18642,2036 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST01-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>非 admin は 403 拒否表示</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>一般ユーザー</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」(role=alert)・データ非表示</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>TC1 実サインアップユーザーで実証</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST01-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>管理シェル (ダークサイドバー) がモック準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin を開く</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>ADMIN CONSOLE・運営タグ・6 項目ナビ</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC2。**監査前は共通シェルが無く 6 画面間の導線ゼロ**</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST01-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>整合性</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>KPI が API=DB (admin 所属 WS 範囲) と一致</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. KPI と psql を突合</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>契約 (T-A-41) 通り所属 WS 範囲の実数</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TC3。全 DB 数との差は契約仕様 (備考に明記)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST01-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>KPI 4 種 (WS/プロジェクト/AI社員/監査イベント24h)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. bento を目視</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>4 タイル表示</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC4。**監査前は audit_log_count_24h が未表示 (API は返していた)**</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST01-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>アクティビティ actor がメール表示</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 一覧を目視</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>生 UUID を出さない (/admin/users で解決、未解決時は短縮 ID)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC5。**監査前は生 UUID 羅列 (鉄則5)**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ST01-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ナビから他 5 画面へ遷移</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 各ナビをクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>全画面到達・active 表示</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TC6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ST01-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし・モバイルナビ操作可</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 390 で操作</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>KPI 2×2・チップナビで遷移</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TC17-18 + 目視</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ST01-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>運営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ミッションヒーロー/トレンド/健全性/コスト等は未描画</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. 目視</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>ダミー業務数値 (100社獲得/¥906 等) の虚偽表示をしない</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>GAP-019 起票 (実データ供給時に実装)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST02-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>一覧が実データ (登録スキル数・active バッジ)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/skills</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>skills テーブルの実数</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実走 (24 件)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST02-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>新規登録 → 一覧反映 + DB</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 新規アップロード 2. name/version/本文 3. 登録</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>POST /admin/skills 201 → 一覧 + DB 行</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC7 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST02-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>**重複登録 (name+version) が 409 明示エラー**</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>同名同版が存在</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 同じ内容で登録</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>「同じ名前・バージョンのスキルが既に存在します」</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TC7b。**v2 実バグ修正: 旧 API は 500 + 汎用「通信エラー」** (pytest 回帰追加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST02-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>削除 → 一覧から消え DB 反映</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DELETE → 行消滅</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC8 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST02-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>検索・編集・装着 (attach) が実 API</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 各操作</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>PATCH / POST attach 実配線</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>vitest uc42 + 実走 (編集ダイアログ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ST02-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>スキル管理</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST03-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレ</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>一覧が実データ (DB 件数一致)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/templates</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>ai_employee_templates 全 14 件</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>TC9 DB 突合 (rows=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST03-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレ</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>非 admin 403</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 開く</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>拒否表示</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC1 と同ガード (共通コンテナ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST03-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレ</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>シェルナビから到達</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. ナビ</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>遷移 + active</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TC6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST03-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレ</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>編集 UI なし (契約が read-only)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 目視</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>偽の編集ボタンを出さない</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>T-A-42 read-only 契約に忠実</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST03-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>AI 社員テンプレ</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST04-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>一覧に実ユーザー (所属 WS 横断)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/users</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>design-audit@example.com 等の実行行</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST04-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>検索で絞り込み</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に入力</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>一致行のみ表示</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC11 (rows=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST04-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>非 admin 403</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 開く</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>拒否表示</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>共通ガード</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST04-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST05-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>集計カード + ログ表が実データ</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. /admin/audit</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>audit_logs の実行行 (時刻/アクター/アクション/対象/IP)</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>実走</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST05-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>検索で絞り込み (credential 等)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索欄に入力</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>一致行のみ・他アクション消滅</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC12 DB 突合 (cred=4 other=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST05-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>アクター/アクション/日付フィルタが実動</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. select/date 操作</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>クライアント側絞り込み + クリア</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>vitest uc34 + 実走経路</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST05-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>受容差分</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>**単一選択肢の死に WS select を撤去**</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 目視</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>「全 WS」1 個だけの select が無い</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>TC13。v2 で撤去 (Rule 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST05-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>**390px 横スクロールなし (v2 実バグ修正)**</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>集計 2×2・フィルタ折返し・ログ表は自前スクロール</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC18。**監査前は固定 grid で body がはみ出す実バグ**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ST05-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>監査ログ</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>非 admin 403</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>拒否表示</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>共通ガード</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ST06-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>運営ナレッジ</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>新規追加 → 一覧 + DB</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. 新規追加 2. タイトル/カテゴリ/本文 3. 追加</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>POST /admin/knowledge → knowledge_nodes 行</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>TC14 DB 突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ST06-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>運営ナレッジ</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ツリー表示トグル → DB 反転</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>行あり</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. switch をクリック</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>PATCH visible_in_tree が実反転</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>TC15 DB 突合 (f→t)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ST06-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>運営ナレッジ</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>登録・編集</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>**削除 (2 段階確認) → DB 反映**</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>行あり</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. 削除 → 削除する</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>DELETE /admin/knowledge/{id} → 論理削除</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TC16。**v2 で実装 — DELETE API があるのに UI 断線 (削除ボタン不在) だった**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ST06-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>運営ナレッジ</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>非 admin 403</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. 開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>拒否表示</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>共通ガード</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ST06-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>運営ナレッジ</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>390px 横スクロールなし</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. 390</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>崩れなし</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -19238,7 +21388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20175,7 +22325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20746,1348 +22896,6 @@
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. プロジェクト切替 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /projects?workspace_id が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /projects?workspace_id が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（現在WS内プロジェクト）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで プロジェクト切替 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. 「Project picker」を選択</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC39-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>プロジェクト切替</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>I4-S（全体で死リンク0確認済）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>テスト観点</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>テスト項目</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>操作手順</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>画面表示</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. グローバル検索 を開く</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>視覚忠実度</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>配色/角丸/タイポが design token 準拠</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面を目視</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>データ取得</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>loading skeleton 表示（横断検索）</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>取得未完</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. グローバル検索 を開き取得完了前を観察</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>空データ</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0 件時の空状態（横断検索）</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GET /search?q=&amp;kind= が空配列</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. データ0件で開く</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>セクションH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>エラー</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>取得失敗の inline error + toast（横断検索）</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>GET /search?q=&amp;kind= が 5xx</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. API を 500 でモックし開く</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>role=alert の inline error 表示 かつ toast 発火</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>UNWANTED critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>権限</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>403 拒否表示（横断検索）</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>権限なしユーザ</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限なしで グローバル検索 を開く</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>セクションG 越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>入力フォーム</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>初期値/placeholder（キーワード）</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. フォームを開く</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>キーワード の初期値/placeholder が正しい</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>バリデーション</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>キーワード: 必須(空で未検索)</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. キーワード に不正値/未入力を入れる</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>エラー表示 かつ 送信ボタン無効</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>インタラクション</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>「検索入力」を操作すると動作する（死にボタン検査）</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>1. 「検索入力」を入力(debounce)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>GET /search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>死にボタン</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>R-T08</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>RLS で可視性担保</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1. 検索実行</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>RLS 内のみヒット(越境自動除外)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>越境</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>a11y</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>axe scan で 0 critical/serious</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>1. axe を実行</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>critical/serious 違反 0（semantic role/aria）</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>vitest-axe 実測済(該当時)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>レスポンシブ</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>320/768/1024/1440 で崩れない</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>1. 各幅で開く</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>横スクロール/はみ出し/縦折れが無い</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>状態永続</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>F5 リロードでログアウトに飛ばない</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>ログイン済</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面で F5</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>セクションG G4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>TUC40-015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>グローバル検索</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>到達性</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>I4-S（全体で死リンク0確認済）</t>
         </is>
@@ -23008,6 +23816,1348 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. プロジェクト切替 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /projects?workspace_id が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（現在WS内プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで プロジェクト切替 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>「Project picker」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. 「Project picker」を選択</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>localStorage(atelier_current_project) 永続化（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC39-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>プロジェクト切替</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>テスト項目</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>画面表示</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>画面が正常表示（全 UI 要素・モック準拠）</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開く</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>モックの全要素（見出し/ボタン/一覧/フォーム）が表示される</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>視覚忠実度</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>配色/角丸/タイポが design token 準拠</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面を目視</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>--color-* / --rounded-* / --text-* トークンで描画（ハードコード色なし）</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>段1: token値=DESIGN-atelier.md 一致(済)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>データ取得</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>loading skeleton 表示（横断検索）</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>取得未完</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. グローバル検索 を開き取得完了前を観察</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>&lt;Loading&gt;（role=status/aria-live）が出る</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>空データ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0 件時の空状態（横断検索）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>GET /search?q=&amp;kind= が空配列</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. データ0件で開く</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>空状態メッセージを表示（500/undefined 参照にならない）</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>セクションH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>取得失敗の inline error + toast（横断検索）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>GET /search?q=&amp;kind= が 5xx</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. API を 500 でモックし開く</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>role=alert の inline error 表示 かつ toast 発火</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>UNWANTED critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>権限</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>403 拒否表示（横断検索）</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>権限なしユーザ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限なしで グローバル検索 を開く</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>「権限がありません」等の拒否表示（他人のデータは出さない=RLS）</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>セクションG 越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>入力フォーム</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>初期値/placeholder（キーワード）</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. フォームを開く</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>キーワード の初期値/placeholder が正しい</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>バリデーション</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>キーワード: 必須(空で未検索)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. キーワード に不正値/未入力を入れる</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>エラー表示 かつ 送信ボタン無効</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>「種別フィルタ(all/project/task/knowledge/employee)」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. 「種別フィルタ(all/project/task/knowledge/employee)」を各クリック</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>kind を切替して再検索（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>インタラクション</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>「検索入力」を操作すると動作する（死にボタン検査）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>1. 「検索入力」を入力(debounce)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>GET /search を叩き結果を種別ラベル付きで表示（onClick/href/API が実在し、押すと副作用が起きる）</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>死にボタン</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>R-T08</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>RLS で可視性担保</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>1. 検索実行</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>RLS 内のみヒット(越境自動除外)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>越境</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>a11y</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>axe scan で 0 critical/serious</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>1. axe を実行</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>critical/serious 違反 0（semantic role/aria）</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>vitest-axe 実測済(該当時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>レスポンシブ</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>320/768/1024/1440 で崩れない</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>1. 各幅で開く</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>横スクロール/はみ出し/縦折れが無い</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Playwright responsive.e2e 26画面×4幅 実走 第8軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>状態永続</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>F5 リロードでログアウトに飛ばない</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面で F5</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>保護ガードで維持・状態復元（URL クエリ等）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>セクションG G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TUC40-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>グローバル検索</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>到達性</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ナビ/リンクからUIで到達でき遷移先が正しい</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1. 導線から本画面へ到達→主要リンクを辿る</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>死リンク無し・遷移先が正しい文脈(param)で開く</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>I4-S（全体で死リンク0確認済）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
